--- a/docs/HX3_FPGA_SPI.xlsx
+++ b/docs/HX3_FPGA_SPI.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="275">
   <si>
     <t>Name</t>
   </si>
@@ -381,15 +381,9 @@
     <t>Tuning Vals</t>
   </si>
   <si>
-    <t>1024x2</t>
-  </si>
-  <si>
     <t>512x2</t>
   </si>
   <si>
-    <t>128x2</t>
-  </si>
-  <si>
     <t>8192x2</t>
   </si>
   <si>
@@ -771,7 +765,85 @@
     <t>VIB PreEmph</t>
   </si>
   <si>
-    <t>512x4</t>
+    <t>1024 x4</t>
+  </si>
+  <si>
+    <t>512 x4</t>
+  </si>
+  <si>
+    <t>8192 x2</t>
+  </si>
+  <si>
+    <t>96 x2</t>
+  </si>
+  <si>
+    <t>1024 x2</t>
+  </si>
+  <si>
+    <t>512 x2</t>
+  </si>
+  <si>
+    <t>128 x2</t>
+  </si>
+  <si>
+    <t>2048 x4</t>
+  </si>
+  <si>
+    <t>FPGA</t>
+  </si>
+  <si>
+    <t>firmware</t>
+  </si>
+  <si>
+    <t>Buffer für Update</t>
+  </si>
+  <si>
+    <t>failsafe_base</t>
+  </si>
+  <si>
+    <t>update_info</t>
+  </si>
+  <si>
+    <t>Board Info</t>
+  </si>
+  <si>
+    <t>MIDI CC Base</t>
+  </si>
+  <si>
+    <t>Organ Model Base</t>
+  </si>
+  <si>
+    <t>Speaker Model Base</t>
+  </si>
+  <si>
+    <t>Preset Base</t>
+  </si>
+  <si>
+    <t>100 Blöcke</t>
+  </si>
+  <si>
+    <t>16 Blöcke</t>
+  </si>
+  <si>
+    <t>Sicherungskopie</t>
+  </si>
+  <si>
+    <t>Update List</t>
+  </si>
+  <si>
+    <t>Filterkoeffizienten</t>
+  </si>
+  <si>
+    <t>8 Wavesets</t>
+  </si>
+  <si>
+    <t>4 Taperings</t>
+  </si>
+  <si>
+    <t>HX3 Edit Array</t>
+  </si>
+  <si>
+    <t>XC6S25 Binary, 196 Blöcke</t>
   </si>
 </sst>
 </file>
@@ -1324,10 +1396,10 @@
       <c r="E1" s="18"/>
       <c r="F1" s="18"/>
       <c r="L1" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2" spans="1:18" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
@@ -1344,16 +1416,16 @@
         <v>7</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>111</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>112</v>
@@ -1390,20 +1462,20 @@
         <v>0</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>125</v>
+        <v>255</v>
       </c>
       <c r="N3" s="5">
         <v>32</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="Q3" s="17" t="str">
-        <f>CONCATENATE("#define LCTARGET_",UPPER(SUBSTITUTE(O3," ","_"))," ",L3)</f>
-        <v>#define LCTARGET_SCAN_DRIVER 0</v>
+        <f>CONCATENATE("#define LCTARGET_",UPPER(SUBSTITUTE(O3," ","_"))," ",L3,"  // ",P3)</f>
+        <v>#define LCTARGET_SCAN_DRIVER 0  // aus DataFlash</v>
       </c>
       <c r="R3" s="21" t="str">
         <f>CONCATENATE("  c_lctarget_",LOWER(SUBSTITUTE(O3," ","_"))," = ",L3,";")</f>
@@ -1435,7 +1507,7 @@
         <v>1</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>124</v>
+        <v>248</v>
       </c>
       <c r="N4" s="5">
         <v>32</v>
@@ -1444,11 +1516,11 @@
         <v>113</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="Q4" s="17" t="str">
-        <f t="shared" ref="Q4:Q16" si="2">CONCATENATE("#define LCTARGET_",UPPER(SUBSTITUTE(O4," ","_"))," ",L4)</f>
-        <v>#define LCTARGET_TAPERING 1</v>
+        <f t="shared" ref="Q4:Q16" si="2">CONCATENATE("#define LCTARGET_",UPPER(SUBSTITUTE(O4," ","_"))," ",L4,"  // ",P4)</f>
+        <v>#define LCTARGET_TAPERING 1  // aus DataFlash</v>
       </c>
       <c r="R4" s="21" t="str">
         <f t="shared" ref="R4:R16" si="3">CONCATENATE("  c_lctarget_",LOWER(SUBSTITUTE(O4," ","_"))," = ",L4,";")</f>
@@ -1480,20 +1552,20 @@
         <v>2</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="N5" s="5">
         <v>32</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="Q5" s="17" t="str">
         <f t="shared" si="2"/>
-        <v>#define LCTARGET_FIR_COEFF 2</v>
+        <v>#define LCTARGET_FIR_COEFF 2  // aus DataFlash</v>
       </c>
       <c r="R5" s="21" t="str">
         <f t="shared" si="3"/>
@@ -1531,11 +1603,11 @@
         <v>117</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Q6" s="17" t="str">
         <f t="shared" si="2"/>
-        <v>#define LCTARGET_KEYMAP 3</v>
+        <v>#define LCTARGET_KEYMAP 3  // berechnet</v>
       </c>
       <c r="R6" s="21" t="str">
         <f t="shared" si="3"/>
@@ -1568,20 +1640,20 @@
         <v>4</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>123</v>
+        <v>250</v>
       </c>
       <c r="N7" s="5">
         <v>16</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="Q7" s="17" t="str">
         <f t="shared" si="2"/>
-        <v>#define LCTARGET_WAVESET 4</v>
+        <v>#define LCTARGET_WAVESET 4  // aus DataFlash</v>
       </c>
       <c r="R7" s="21" t="str">
         <f t="shared" si="3"/>
@@ -1594,7 +1666,7 @@
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D8" s="5">
         <v>8</v>
@@ -1608,11 +1680,14 @@
         <v xml:space="preserve">  c_spi_scan_midich = 4;</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L8" s="5">
         <v>5</v>
       </c>
+      <c r="M8" s="5" t="s">
+        <v>251</v>
+      </c>
       <c r="N8" s="5">
         <v>16</v>
       </c>
@@ -1620,11 +1695,11 @@
         <v>119</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Q8" s="17" t="str">
         <f t="shared" si="2"/>
-        <v>#define LCTARGET_TUNING_VALS 5</v>
+        <v>#define LCTARGET_TUNING_VALS 5  // berechnet</v>
       </c>
       <c r="R8" s="21" t="str">
         <f t="shared" si="3"/>
@@ -1636,7 +1711,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D9" s="5">
         <v>8</v>
@@ -1653,20 +1728,20 @@
         <v>6</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>120</v>
+        <v>252</v>
       </c>
       <c r="N9" s="5">
         <v>16</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Q9" s="17" t="str">
         <f t="shared" si="2"/>
-        <v>#define LCTARGET_HP_FILTER 6</v>
+        <v>#define LCTARGET_HP_FILTER 6  // berechnet</v>
       </c>
       <c r="R9" s="21" t="str">
         <f t="shared" si="3"/>
@@ -1678,7 +1753,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D10" s="5">
         <v>8</v>
@@ -1692,13 +1767,13 @@
         <v xml:space="preserve">  c_spi_scan_splitmode = 6;</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="L10" s="5">
         <v>7</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>121</v>
+        <v>253</v>
       </c>
       <c r="N10" s="5">
         <v>16</v>
@@ -1707,11 +1782,11 @@
         <v>118</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Q10" s="17" t="str">
         <f t="shared" si="2"/>
-        <v>#define LCTARGET_TUBE_AMP_SLOPE 7</v>
+        <v>#define LCTARGET_TUBE_AMP_SLOPE 7  // berechnet</v>
       </c>
       <c r="R10" s="21" t="str">
         <f t="shared" si="3"/>
@@ -1723,7 +1798,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D11" s="5">
         <v>8</v>
@@ -1749,11 +1824,11 @@
         <v>1</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Q11" s="17" t="str">
         <f t="shared" si="2"/>
-        <v>#define LCTARGET_UPPER_DRAWBARS 8</v>
+        <v>#define LCTARGET_UPPER_DRAWBARS 8  // berechnet</v>
       </c>
       <c r="R11" s="21" t="str">
         <f t="shared" si="3"/>
@@ -1765,7 +1840,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D12" s="5">
         <v>8</v>
@@ -1779,7 +1854,7 @@
         <v xml:space="preserve">  c_spi_scan_splitpoint = 8;</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="L12" s="5">
         <v>9</v>
@@ -1794,11 +1869,11 @@
         <v>2</v>
       </c>
       <c r="P12" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Q12" s="17" t="str">
         <f t="shared" si="2"/>
-        <v>#define LCTARGET_LOWER_DRAWBARS 9</v>
+        <v>#define LCTARGET_LOWER_DRAWBARS 9  // berechnet</v>
       </c>
       <c r="R12" s="21" t="str">
         <f t="shared" si="3"/>
@@ -1810,7 +1885,7 @@
         <v>9</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D13" s="5">
         <v>8</v>
@@ -1824,7 +1899,7 @@
         <v xml:space="preserve">  c_spi_scan_click = 9;</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L13" s="5">
         <v>10</v>
@@ -1839,11 +1914,11 @@
         <v>3</v>
       </c>
       <c r="P13" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Q13" s="17" t="str">
         <f t="shared" si="2"/>
-        <v>#define LCTARGET_PEDAL_DRAWBARS 10</v>
+        <v>#define LCTARGET_PEDAL_DRAWBARS 10  // berechnet</v>
       </c>
       <c r="R13" s="21" t="str">
         <f t="shared" si="3"/>
@@ -1855,7 +1930,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D14" s="5">
         <v>8</v>
@@ -1869,13 +1944,13 @@
         <v xml:space="preserve">  c_spi_scan_key_transpose = 10;</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L14" s="5">
         <v>11</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>122</v>
+        <v>254</v>
       </c>
       <c r="N14" s="5">
         <v>16</v>
@@ -1884,11 +1959,11 @@
         <v>114</v>
       </c>
       <c r="P14" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Q14" s="17" t="str">
         <f t="shared" si="2"/>
-        <v>#define LCTARGET_ADSR_UPPER 11</v>
+        <v>#define LCTARGET_ADSR_UPPER 11  // berechnet</v>
       </c>
       <c r="R14" s="21" t="str">
         <f t="shared" si="3"/>
@@ -1900,7 +1975,7 @@
         <v>11</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D15" s="5">
         <v>8</v>
@@ -1914,13 +1989,13 @@
         <v xml:space="preserve">  c_spi_scan_config_1 = 11;</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L15" s="5">
         <v>12</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>122</v>
+        <v>254</v>
       </c>
       <c r="N15" s="5">
         <v>16</v>
@@ -1929,11 +2004,11 @@
         <v>115</v>
       </c>
       <c r="P15" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Q15" s="17" t="str">
         <f t="shared" si="2"/>
-        <v>#define LCTARGET_ADSR_LOWER 12</v>
+        <v>#define LCTARGET_ADSR_LOWER 12  // berechnet</v>
       </c>
       <c r="R15" s="21" t="str">
         <f t="shared" si="3"/>
@@ -1945,7 +2020,7 @@
         <v>12</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D16" s="5">
         <v>8</v>
@@ -1959,13 +2034,13 @@
         <v xml:space="preserve">  c_spi_scan_gen_transpose = 12;</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="L16" s="5">
         <v>13</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>122</v>
+        <v>254</v>
       </c>
       <c r="N16" s="5">
         <v>16</v>
@@ -1974,11 +2049,11 @@
         <v>116</v>
       </c>
       <c r="P16" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Q16" s="17" t="str">
         <f t="shared" si="2"/>
-        <v>#define LCTARGET_ADSR_PEDAL 13</v>
+        <v>#define LCTARGET_ADSR_PEDAL 13  // berechnet</v>
       </c>
       <c r="R16" s="21" t="str">
         <f t="shared" si="3"/>
@@ -1990,7 +2065,7 @@
         <v>13</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D17" s="5">
         <v>8</v>
@@ -2007,7 +2082,7 @@
         <v>14</v>
       </c>
       <c r="O17" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
@@ -2015,7 +2090,7 @@
         <v>14</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D18" s="5">
         <v>8</v>
@@ -2029,13 +2104,13 @@
         <v xml:space="preserve">  c_spi_scan_pwm_localdisables = 14;</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L18" s="5">
         <v>15</v>
       </c>
       <c r="O18" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.2">
@@ -2043,7 +2118,7 @@
         <v>15</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D19" s="5">
         <v>8</v>
@@ -2057,7 +2132,7 @@
         <v xml:space="preserve">  c_spi_scan_pwm_auxport_leds = 15;</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="15" x14ac:dyDescent="0.25">
@@ -2065,12 +2140,12 @@
         <v>16</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="15" x14ac:dyDescent="0.25">
       <c r="L21" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>112</v>
@@ -2084,21 +2159,27 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="L22" s="5">
-        <v>944</v>
+        <v>0</v>
+      </c>
+      <c r="M22" s="5">
+        <v>802816</v>
       </c>
       <c r="N22" s="5">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="O22" s="5" t="s">
-        <v>225</v>
+        <v>256</v>
+      </c>
+      <c r="P22" s="5" t="s">
+        <v>274</v>
       </c>
       <c r="Q22" s="17" t="str">
-        <f>CONCATENATE("#define BLOCK_",UPPER(SUBSTITUTE(O22," ","_"))," ",L22)</f>
-        <v>#define BLOCK_CORE_BASE 944</v>
+        <f>CONCATENATE("#define BLOCK_",UPPER(SUBSTITUTE(O22," ","_"))," ",L22,"  // ",P22)</f>
+        <v>#define BLOCK_FPGA 0  // XC6S25 Binary, 196 Blöcke</v>
       </c>
       <c r="R22" s="21" t="str">
-        <f>CONCATENATE("  c_",LOWER(SUBSTITUTE(O22," ","_")),": Word = ",L22,";")</f>
-        <v xml:space="preserve">  c_core_base: Word = 944;</v>
+        <f>CONCATENATE("  c_",LOWER(SUBSTITUTE(O22," ","_")),": Word = ",L22,";  // ",P22)</f>
+        <v xml:space="preserve">  c_fpga: Word = 0;  // XC6S25 Binary, 196 Blöcke</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.2">
@@ -2106,24 +2187,24 @@
         <v>31</v>
       </c>
       <c r="L23" s="5">
-        <v>944</v>
-      </c>
-      <c r="M23" s="5" t="s">
-        <v>125</v>
+        <v>320</v>
       </c>
       <c r="N23" s="5">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="O23" s="5" t="s">
-        <v>226</v>
+        <v>259</v>
+      </c>
+      <c r="P23" s="5" t="s">
+        <v>268</v>
       </c>
       <c r="Q23" s="17" t="str">
-        <f t="shared" ref="Q23:Q41" si="6">CONCATENATE("#define BLOCK_",UPPER(SUBSTITUTE(O23," ","_"))," ",L23)</f>
-        <v>#define BLOCK_SCAN 944</v>
+        <f t="shared" ref="Q23:Q50" si="6">CONCATENATE("#define BLOCK_",UPPER(SUBSTITUTE(O23," ","_"))," ",L23,"  // ",P23)</f>
+        <v>#define BLOCK_FAILSAFE_BASE 320  // Sicherungskopie</v>
       </c>
       <c r="R23" s="21" t="str">
-        <f t="shared" ref="R23:R41" si="7">CONCATENATE("  c_",LOWER(SUBSTITUTE(O23," ","_")),": Word = ",L23,";")</f>
-        <v xml:space="preserve">  c_scan: Word = 944;</v>
+        <f t="shared" ref="R23:R50" si="7">CONCATENATE("  c_",LOWER(SUBSTITUTE(O23," ","_")),": Word = ",L23,";  // ",P23)</f>
+        <v xml:space="preserve">  c_failsafe_base: Word = 320;  // Sicherungskopie</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.2">
@@ -2145,25 +2226,21 @@
         <v xml:space="preserve">  c_spi_perc_ena = 32;</v>
       </c>
       <c r="L24" s="5">
-        <f>L23+2</f>
-        <v>946</v>
-      </c>
-      <c r="M24" s="5">
-        <v>4096</v>
-      </c>
-      <c r="N24" s="5">
-        <v>8</v>
+        <v>637</v>
       </c>
       <c r="O24" s="5" t="s">
-        <v>227</v>
+        <v>260</v>
+      </c>
+      <c r="P24" s="5" t="s">
+        <v>269</v>
       </c>
       <c r="Q24" s="17" t="str">
         <f t="shared" si="6"/>
-        <v>#define BLOCK_VOICE 946</v>
+        <v>#define BLOCK_UPDATE_INFO 637  // Update List</v>
       </c>
       <c r="R24" s="21" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">  c_voice: Word = 946;</v>
+        <v xml:space="preserve">  c_update_info: Word = 637;  // Update List</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.2">
@@ -2185,25 +2262,18 @@
         <v xml:space="preserve">  c_spi_perc_vol = 33;</v>
       </c>
       <c r="L25" s="5">
-        <f>L22+3</f>
-        <v>947</v>
-      </c>
-      <c r="M25" s="5">
-        <v>4096</v>
-      </c>
-      <c r="N25" s="5">
-        <v>8</v>
+        <v>639</v>
       </c>
       <c r="O25" s="5" t="s">
-        <v>228</v>
+        <v>261</v>
       </c>
       <c r="Q25" s="17" t="str">
         <f t="shared" si="6"/>
-        <v>#define BLOCK_DEFAULTS 947</v>
+        <v xml:space="preserve">#define BLOCK_BOARD_INFO 639  // </v>
       </c>
       <c r="R25" s="21" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">  c_defaults: Word = 947;</v>
+        <v xml:space="preserve">  c_board_info: Word = 639;  // </v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.2">
@@ -2211,7 +2281,7 @@
         <v>34</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D26" s="5">
         <v>16</v>
@@ -2225,27 +2295,24 @@
         <v xml:space="preserve">  c_spi_upper_wet_lvl = 34;</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L26" s="5">
-        <v>953</v>
-      </c>
-      <c r="M26" s="5">
-        <v>4096</v>
-      </c>
-      <c r="N26" s="5">
-        <v>8</v>
+        <v>768</v>
       </c>
       <c r="O26" s="5" t="s">
-        <v>229</v>
+        <v>264</v>
+      </c>
+      <c r="P26" s="5" t="s">
+        <v>267</v>
       </c>
       <c r="Q26" s="17" t="str">
         <f t="shared" si="6"/>
-        <v>#define BLOCK_EEPROM 953</v>
+        <v>#define BLOCK_SPEAKER_MODEL_BASE 768  // 16 Blöcke</v>
       </c>
       <c r="R26" s="21" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">  c_eeprom: Word = 953;</v>
+        <v xml:space="preserve">  c_speaker_model_base: Word = 768;  // 16 Blöcke</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.2">
@@ -2267,22 +2334,21 @@
         <v xml:space="preserve">  c_spi_lower_lvl = 35;</v>
       </c>
       <c r="L27" s="5">
-        <f>L22+11</f>
-        <v>955</v>
-      </c>
-      <c r="N27" s="5">
-        <v>32</v>
+        <v>784</v>
       </c>
       <c r="O27" s="5" t="s">
-        <v>230</v>
+        <v>263</v>
+      </c>
+      <c r="P27" s="5" t="s">
+        <v>267</v>
       </c>
       <c r="Q27" s="17" t="str">
         <f t="shared" si="6"/>
-        <v>#define BLOCK_TAPER_BASE 955</v>
+        <v>#define BLOCK_ORGAN_MODEL_BASE 784  // 16 Blöcke</v>
       </c>
       <c r="R27" s="21" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">  c_taper_base: Word = 955;</v>
+        <v xml:space="preserve">  c_organ_model_base: Word = 784;  // 16 Blöcke</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.2">
@@ -2304,25 +2370,21 @@
         <v xml:space="preserve">  c_spi_pedal_lvl = 36;</v>
       </c>
       <c r="L28" s="5">
-        <f>L23+11</f>
-        <v>955</v>
-      </c>
-      <c r="M28" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="N28" s="5">
-        <v>32</v>
+        <v>800</v>
       </c>
       <c r="O28" s="5" t="s">
-        <v>213</v>
+        <v>265</v>
+      </c>
+      <c r="P28" s="5" t="s">
+        <v>266</v>
       </c>
       <c r="Q28" s="17" t="str">
         <f t="shared" si="6"/>
-        <v>#define BLOCK_TAPER_0 955</v>
+        <v>#define BLOCK_PRESET_BASE 800  // 100 Blöcke</v>
       </c>
       <c r="R28" s="21" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">  c_taper_0: Word = 955;</v>
+        <v xml:space="preserve">  c_preset_base: Word = 800;  // 100 Blöcke</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.2">
@@ -2330,7 +2392,7 @@
         <v>37</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D29" s="5">
         <v>16</v>
@@ -2344,28 +2406,24 @@
         <v xml:space="preserve">  c_spi_upper_dry_lvl = 37;</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L29" s="5">
-        <f>L28+1</f>
-        <v>956</v>
-      </c>
-      <c r="M29" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="N29" s="5">
-        <v>32</v>
+        <v>928</v>
       </c>
       <c r="O29" s="5" t="s">
-        <v>214</v>
+        <v>262</v>
+      </c>
+      <c r="P29" s="5" t="s">
+        <v>267</v>
       </c>
       <c r="Q29" s="17" t="str">
         <f t="shared" si="6"/>
-        <v>#define BLOCK_TAPER_1 956</v>
+        <v>#define BLOCK_MIDI_CC_BASE 928  // 16 Blöcke</v>
       </c>
       <c r="R29" s="21" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">  c_taper_1: Word = 956;</v>
+        <v xml:space="preserve">  c_midi_cc_base: Word = 928;  // 16 Blöcke</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.2">
@@ -2387,25 +2445,21 @@
         <v xml:space="preserve">  c_spi_perc_precharge_time = 38;</v>
       </c>
       <c r="L30" s="5">
-        <f t="shared" ref="L30:L31" si="10">L29+1</f>
-        <v>957</v>
-      </c>
-      <c r="M30" s="5" t="s">
-        <v>124</v>
+        <v>944</v>
       </c>
       <c r="N30" s="5">
         <v>32</v>
       </c>
       <c r="O30" s="5" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="Q30" s="17" t="str">
         <f t="shared" si="6"/>
-        <v>#define BLOCK_TAPER_2 957</v>
+        <v xml:space="preserve">#define BLOCK_CORE_BASE 944  // </v>
       </c>
       <c r="R30" s="21" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">  c_taper_2: Word = 957;</v>
+        <v xml:space="preserve">  c_core_base: Word = 944;  // </v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.2">
@@ -2427,25 +2481,24 @@
         <v xml:space="preserve">  c_spi_perc_decay_time = 39;</v>
       </c>
       <c r="L31" s="5">
-        <f t="shared" si="10"/>
-        <v>958</v>
+        <v>944</v>
       </c>
       <c r="M31" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N31" s="5">
         <v>32</v>
       </c>
       <c r="O31" s="5" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="Q31" s="17" t="str">
         <f t="shared" si="6"/>
-        <v>#define BLOCK_TAPER_3 958</v>
+        <v xml:space="preserve">#define BLOCK_SCAN 944  // </v>
       </c>
       <c r="R31" s="21" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">  c_taper_3: Word = 958;</v>
+        <v xml:space="preserve">  c_scan: Word = 944;  // </v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.2">
@@ -2467,28 +2520,28 @@
         <v xml:space="preserve">  c_spi_upper_bb_mech_cont_ena = 40;</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L32" s="5">
-        <f>L22+15</f>
-        <v>959</v>
-      </c>
-      <c r="M32" s="5" t="s">
-        <v>121</v>
+        <f>L31+2</f>
+        <v>946</v>
+      </c>
+      <c r="M32" s="5">
+        <v>4096</v>
       </c>
       <c r="N32" s="5">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O32" s="5" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="Q32" s="17" t="str">
         <f t="shared" si="6"/>
-        <v>#define BLOCK_FIR_COEFF 959</v>
+        <v xml:space="preserve">#define BLOCK_VOICE 946  // </v>
       </c>
       <c r="R32" s="21" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">  c_fir_coeff: Word = 959;</v>
+        <v xml:space="preserve">  c_voice: Word = 946;  // </v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.2">
@@ -2510,24 +2563,31 @@
         <v xml:space="preserve">  c_spi_upper_bb_adsr_ena = 41;</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="L33" s="5">
-        <v>960</v>
+        <f>L30+3</f>
+        <v>947</v>
+      </c>
+      <c r="M33" s="5">
+        <v>4096</v>
       </c>
       <c r="N33" s="5">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O33" s="5" t="s">
-        <v>231</v>
+        <v>226</v>
+      </c>
+      <c r="P33" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="Q33" s="17" t="str">
         <f t="shared" si="6"/>
-        <v>#define BLOCK_WAVESET_BASE 960</v>
+        <v>#define BLOCK_DEFAULTS 947  // HX3 Edit Array</v>
       </c>
       <c r="R33" s="21" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">  c_waveset_base: Word = 960;</v>
+        <v xml:space="preserve">  c_defaults: Word = 947;  // HX3 Edit Array</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.2">
@@ -2549,27 +2609,27 @@
         <v xml:space="preserve">  c_spi_upper_bb_harp_sust_ena = 42;</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="L34" s="5">
-        <v>960</v>
-      </c>
-      <c r="M34" s="5" t="s">
-        <v>123</v>
+        <v>953</v>
+      </c>
+      <c r="M34" s="5">
+        <v>4096</v>
       </c>
       <c r="N34" s="5">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O34" s="5" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="Q34" s="17" t="str">
         <f t="shared" si="6"/>
-        <v>#define BLOCK_WAVESET_0 960</v>
+        <v xml:space="preserve">#define BLOCK_EEPROM 953  // </v>
       </c>
       <c r="R34" s="21" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">  c_waveset_0: Word = 960;</v>
+        <v xml:space="preserve">  c_eeprom: Word = 953;  // </v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.2">
@@ -2591,28 +2651,28 @@
         <v xml:space="preserve">  c_spi_upper_bb_to_dry_ena = 43;</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L35" s="5">
-        <f>L34+4</f>
-        <v>964</v>
-      </c>
-      <c r="M35" s="5" t="s">
-        <v>123</v>
+        <f>L30+11</f>
+        <v>955</v>
       </c>
       <c r="N35" s="5">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="O35" s="5" t="s">
-        <v>218</v>
+        <v>228</v>
+      </c>
+      <c r="P35" s="5" t="s">
+        <v>272</v>
       </c>
       <c r="Q35" s="17" t="str">
         <f t="shared" si="6"/>
-        <v>#define BLOCK_WAVESET_1 964</v>
+        <v>#define BLOCK_TAPER_BASE 955  // 4 Taperings</v>
       </c>
       <c r="R35" s="21" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">  c_waveset_1: Word = 964;</v>
+        <v xml:space="preserve">  c_taper_base: Word = 955;  // 4 Taperings</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.2">
@@ -2634,28 +2694,28 @@
         <v xml:space="preserve">  c_spi_lower_bb_adsr_ena = 44;</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="L36" s="5">
-        <f t="shared" ref="L36:L41" si="11">L35+4</f>
-        <v>968</v>
+        <f>L31+11</f>
+        <v>955</v>
       </c>
       <c r="M36" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N36" s="5">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="O36" s="5" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="Q36" s="17" t="str">
         <f t="shared" si="6"/>
-        <v>#define BLOCK_WAVESET_2 968</v>
+        <v xml:space="preserve">#define BLOCK_TAPER_0 955  // </v>
       </c>
       <c r="R36" s="21" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">  c_waveset_2: Word = 968;</v>
+        <v xml:space="preserve">  c_taper_0: Word = 955;  // </v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.2">
@@ -2677,28 +2737,28 @@
         <v xml:space="preserve">  c_spi_ped_to_vib_lvl = 45;</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="L37" s="5">
-        <f t="shared" si="11"/>
-        <v>972</v>
+        <f>L36+1</f>
+        <v>956</v>
       </c>
       <c r="M37" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N37" s="5">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="O37" s="5" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="Q37" s="17" t="str">
         <f t="shared" si="6"/>
-        <v>#define BLOCK_WAVESET_3 972</v>
+        <v xml:space="preserve">#define BLOCK_TAPER_1 956  // </v>
       </c>
       <c r="R37" s="21" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">  c_waveset_3: Word = 972;</v>
+        <v xml:space="preserve">  c_taper_1: Word = 956;  // </v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.2">
@@ -2720,28 +2780,28 @@
         <v xml:space="preserve">  c_spi_ped_to_ao28_lvl = 46;</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L38" s="5">
-        <f t="shared" si="11"/>
-        <v>976</v>
+        <f t="shared" ref="L38:L39" si="10">L37+1</f>
+        <v>957</v>
       </c>
       <c r="M38" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N38" s="5">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="O38" s="5" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="Q38" s="17" t="str">
         <f t="shared" si="6"/>
-        <v>#define BLOCK_WAVESET_4 976</v>
+        <v xml:space="preserve">#define BLOCK_TAPER_2 957  // </v>
       </c>
       <c r="R38" s="21" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">  c_waveset_4: Word = 976;</v>
+        <v xml:space="preserve">  c_taper_2: Word = 957;  // </v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.2">
@@ -2763,28 +2823,28 @@
         <v xml:space="preserve">  c_spi_ped_to_bypass_amp = 47;</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="L39" s="5">
-        <f t="shared" si="11"/>
-        <v>980</v>
+        <f t="shared" si="10"/>
+        <v>958</v>
       </c>
       <c r="M39" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N39" s="5">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="O39" s="5" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="Q39" s="17" t="str">
         <f t="shared" si="6"/>
-        <v>#define BLOCK_WAVESET_5 980</v>
+        <v xml:space="preserve">#define BLOCK_TAPER_3 958  // </v>
       </c>
       <c r="R39" s="21" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">  c_waveset_5: Word = 980;</v>
+        <v xml:space="preserve">  c_taper_3: Word = 958;  // </v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.2">
@@ -2793,60 +2853,102 @@
       </c>
       <c r="F40" s="21"/>
       <c r="L40" s="5">
-        <f t="shared" si="11"/>
-        <v>984</v>
+        <f>L30+15</f>
+        <v>959</v>
       </c>
       <c r="M40" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="N40" s="5">
         <v>16</v>
       </c>
       <c r="O40" s="5" t="s">
-        <v>223</v>
+        <v>231</v>
+      </c>
+      <c r="P40" s="5" t="s">
+        <v>270</v>
       </c>
       <c r="Q40" s="17" t="str">
         <f t="shared" si="6"/>
-        <v>#define BLOCK_WAVESET_6 984</v>
+        <v>#define BLOCK_FIR_COEFF 959  // Filterkoeffizienten</v>
       </c>
       <c r="R40" s="21" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">  c_waveset_6: Word = 984;</v>
+        <v xml:space="preserve">  c_fir_coeff: Word = 959;  // Filterkoeffizienten</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.2">
       <c r="F41" s="21"/>
       <c r="L41" s="5">
-        <f t="shared" si="11"/>
-        <v>988</v>
-      </c>
-      <c r="M41" s="5" t="s">
-        <v>123</v>
+        <v>960</v>
       </c>
       <c r="N41" s="5">
         <v>16</v>
       </c>
       <c r="O41" s="5" t="s">
-        <v>224</v>
+        <v>229</v>
+      </c>
+      <c r="P41" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="Q41" s="17" t="str">
         <f t="shared" si="6"/>
-        <v>#define BLOCK_WAVESET_7 988</v>
+        <v>#define BLOCK_WAVESET_BASE 960  // 8 Wavesets</v>
       </c>
       <c r="R41" s="21" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">  c_waveset_7: Word = 988;</v>
+        <v xml:space="preserve">  c_waveset_base: Word = 960;  // 8 Wavesets</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.2">
       <c r="F42" s="21"/>
+      <c r="L42" s="5">
+        <v>960</v>
+      </c>
+      <c r="M42" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="N42" s="5">
+        <v>16</v>
+      </c>
+      <c r="O42" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q42" s="17" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">#define BLOCK_WAVESET_0 960  // </v>
+      </c>
+      <c r="R42" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">  c_waveset_0: Word = 960;  // </v>
+      </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>63</v>
       </c>
       <c r="F43" s="21"/>
-      <c r="Q43" s="17"/>
+      <c r="L43" s="5">
+        <f>L42+4</f>
+        <v>964</v>
+      </c>
+      <c r="M43" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="N43" s="5">
+        <v>16</v>
+      </c>
+      <c r="O43" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q43" s="17" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">#define BLOCK_WAVESET_1 964  // </v>
+      </c>
+      <c r="R43" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">  c_waveset_1: Word = 964;  // </v>
+      </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
@@ -2859,7 +2961,7 @@
         <v>8</v>
       </c>
       <c r="E44" s="17" t="str">
-        <f t="shared" ref="E44:E52" si="12">CONCATENATE("#define SPI_",UPPER(SUBSTITUTE(C44," ","_"))," ",A44)</f>
+        <f t="shared" ref="E44:E52" si="11">CONCATENATE("#define SPI_",UPPER(SUBSTITUTE(C44," ","_"))," ",A44)</f>
         <v>#define SPI_SWAP_DACS 64</v>
       </c>
       <c r="F44" s="21" t="str">
@@ -2867,9 +2969,29 @@
         <v xml:space="preserve">  c_spi_swap_dacs = 64;</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q44" s="17"/>
+        <v>143</v>
+      </c>
+      <c r="L44" s="5">
+        <f t="shared" ref="L44:L49" si="12">L43+4</f>
+        <v>968</v>
+      </c>
+      <c r="M44" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="N44" s="5">
+        <v>16</v>
+      </c>
+      <c r="O44" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q44" s="17" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">#define BLOCK_WAVESET_2 968  // </v>
+      </c>
+      <c r="R44" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">  c_waveset_2: Word = 968;  // </v>
+      </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
@@ -2882,7 +3004,7 @@
         <v>8</v>
       </c>
       <c r="E45" s="17" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>#define SPI_TEST_SEL 65</v>
       </c>
       <c r="F45" s="21" t="str">
@@ -2892,7 +3014,27 @@
       <c r="G45" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="Q45" s="17"/>
+      <c r="L45" s="5">
+        <f t="shared" si="12"/>
+        <v>972</v>
+      </c>
+      <c r="M45" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="N45" s="5">
+        <v>16</v>
+      </c>
+      <c r="O45" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q45" s="17" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">#define BLOCK_WAVESET_3 972  // </v>
+      </c>
+      <c r="R45" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">  c_waveset_3: Word = 972;  // </v>
+      </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
@@ -2905,7 +3047,7 @@
         <v>8</v>
       </c>
       <c r="E46" s="17" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>#define SPI_INSERTS 66</v>
       </c>
       <c r="F46" s="21" t="str">
@@ -2913,11 +3055,31 @@
         <v xml:space="preserve">  c_spi_inserts = 66;</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H46" s="16"/>
       <c r="I46" s="16"/>
-      <c r="Q46" s="17"/>
+      <c r="L46" s="5">
+        <f t="shared" si="12"/>
+        <v>976</v>
+      </c>
+      <c r="M46" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="N46" s="5">
+        <v>16</v>
+      </c>
+      <c r="O46" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q46" s="17" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">#define BLOCK_WAVESET_4 976  // </v>
+      </c>
+      <c r="R46" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">  c_waveset_4: Word = 976;  // </v>
+      </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
@@ -2930,7 +3092,7 @@
         <v>8</v>
       </c>
       <c r="E47" s="17" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>#define SPI_LEAK_RNDMASK 67</v>
       </c>
       <c r="F47" s="21" t="str">
@@ -2938,9 +3100,29 @@
         <v xml:space="preserve">  c_spi_leak_rndmask = 67;</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q47" s="17"/>
+        <v>142</v>
+      </c>
+      <c r="L47" s="5">
+        <f t="shared" si="12"/>
+        <v>980</v>
+      </c>
+      <c r="M47" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="N47" s="5">
+        <v>16</v>
+      </c>
+      <c r="O47" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q47" s="17" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">#define BLOCK_WAVESET_5 980  // </v>
+      </c>
+      <c r="R47" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">  c_waveset_5: Word = 980;  // </v>
+      </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
@@ -2953,7 +3135,7 @@
         <v>8</v>
       </c>
       <c r="E48" s="17" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>#define SPI_DDS_TUNING 68</v>
       </c>
       <c r="F48" s="21" t="str">
@@ -2961,11 +3143,31 @@
         <v xml:space="preserve">  c_spi_dds_tuning = 68;</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q48" s="17"/>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
+        <v>140</v>
+      </c>
+      <c r="L48" s="5">
+        <f t="shared" si="12"/>
+        <v>984</v>
+      </c>
+      <c r="M48" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="N48" s="5">
+        <v>16</v>
+      </c>
+      <c r="O48" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q48" s="17" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">#define BLOCK_WAVESET_6 984  // </v>
+      </c>
+      <c r="R48" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">  c_waveset_6: Word = 984;  // </v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
         <v>69</v>
       </c>
@@ -2976,7 +3178,7 @@
         <v>8</v>
       </c>
       <c r="E49" s="17" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>#define SPI_AMP_IN_LVL 69</v>
       </c>
       <c r="F49" s="21" t="str">
@@ -2984,11 +3186,31 @@
         <v xml:space="preserve">  c_spi_amp_in_lvl = 69;</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q49" s="17"/>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
+        <v>126</v>
+      </c>
+      <c r="L49" s="5">
+        <f t="shared" si="12"/>
+        <v>988</v>
+      </c>
+      <c r="M49" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="N49" s="5">
+        <v>16</v>
+      </c>
+      <c r="O49" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q49" s="17" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">#define BLOCK_WAVESET_7 988  // </v>
+      </c>
+      <c r="R49" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">  c_waveset_7: Word = 988;  // </v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
         <v>70</v>
       </c>
@@ -2999,7 +3221,7 @@
         <v>8</v>
       </c>
       <c r="E50" s="17" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>#define SPI_AMP_OUT_LVL 70</v>
       </c>
       <c r="F50" s="21" t="str">
@@ -3007,11 +3229,33 @@
         <v xml:space="preserve">  c_spi_amp_out_lvl = 70;</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q50" s="17"/>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
+        <v>127</v>
+      </c>
+      <c r="L50" s="5">
+        <v>992</v>
+      </c>
+      <c r="M50" s="5">
+        <v>131072</v>
+      </c>
+      <c r="N50" s="5">
+        <v>8</v>
+      </c>
+      <c r="O50" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="P50" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q50" s="17" t="str">
+        <f t="shared" si="6"/>
+        <v>#define BLOCK_FIRMWARE 992  // Buffer für Update</v>
+      </c>
+      <c r="R50" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">  c_firmware: Word = 992;  // Buffer für Update</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
         <v>71</v>
       </c>
@@ -3022,16 +3266,15 @@
         <v>8</v>
       </c>
       <c r="E51" s="17" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>#define SPI_NC 71</v>
       </c>
       <c r="F51" s="21" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve">  c_spi_nc = 71;</v>
       </c>
-      <c r="Q51" s="17"/>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
         <v>72</v>
       </c>
@@ -3042,7 +3285,7 @@
         <v>8</v>
       </c>
       <c r="E52" s="17" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>#define SPI_MASTER_VOLUME 72</v>
       </c>
       <c r="F52" s="21" t="str">
@@ -3052,31 +3295,29 @@
       <c r="G52" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="Q52" s="17"/>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
         <v>73</v>
       </c>
       <c r="F53" s="21"/>
-      <c r="Q53" s="17"/>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
       <c r="F54" s="21"/>
       <c r="Q54" s="17"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
       <c r="F55" s="21"/>
       <c r="Q55" s="17"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
         <v>79</v>
       </c>
       <c r="F56" s="21"/>
       <c r="Q56" s="17"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A57" s="3">
         <v>80</v>
       </c>
@@ -3095,11 +3336,11 @@
         <v xml:space="preserve">  c_spi_ao28__loudn_bass = 80;</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="Q57" s="17"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
         <v>81</v>
       </c>
@@ -3119,7 +3360,7 @@
       </c>
       <c r="Q58" s="17"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A59" s="3">
         <v>82</v>
       </c>
@@ -3139,7 +3380,7 @@
       </c>
       <c r="Q59" s="17"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A60" s="3">
         <v>83</v>
       </c>
@@ -3159,7 +3400,7 @@
       </c>
       <c r="Q60" s="17"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A61" s="3">
         <v>84</v>
       </c>
@@ -3179,7 +3420,7 @@
       </c>
       <c r="Q61" s="17"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
         <v>85</v>
       </c>
@@ -3198,7 +3439,7 @@
         <v xml:space="preserve">  c_spi_ao28_triode_k2 = 85;</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
         <v>86</v>
       </c>
@@ -3217,7 +3458,7 @@
         <v xml:space="preserve">  c_spi_ao28_pedal_lvl = 86;</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
         <v>87</v>
       </c>
@@ -3303,7 +3544,7 @@
         <v>112</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D71" s="5">
         <v>8</v>
@@ -3322,7 +3563,7 @@
         <v>113</v>
       </c>
       <c r="C72" s="22" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D72" s="5">
         <v>8</v>
@@ -3341,7 +3582,7 @@
         <v>114</v>
       </c>
       <c r="C73" s="22" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D73" s="5">
         <v>8</v>
@@ -3621,7 +3862,7 @@
         <v xml:space="preserve">  c_spi_inc_loadcore = 128;</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
@@ -3643,7 +3884,7 @@
         <v xml:space="preserve">  c_spi_rst_loadcore = 129;</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
@@ -3669,7 +3910,7 @@
         <v>144</v>
       </c>
       <c r="C93" s="23" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D93" s="5">
         <v>8</v>
@@ -3683,7 +3924,7 @@
         <v xml:space="preserve">  c_spi_vib_preemph = 144;</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
@@ -3691,7 +3932,7 @@
         <v>145</v>
       </c>
       <c r="C94" s="23" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D94" s="5">
         <v>8</v>
@@ -3705,7 +3946,7 @@
         <v xml:space="preserve">  c_spi_vib_lc_line_age = 145;</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
@@ -3713,7 +3954,7 @@
         <v>146</v>
       </c>
       <c r="C95" s="23" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D95" s="5">
         <v>8</v>
@@ -3727,7 +3968,7 @@
         <v xml:space="preserve">  c_spi_vib_lc_line_fb = 146;</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
@@ -3735,7 +3976,7 @@
         <v>147</v>
       </c>
       <c r="C96" s="23" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D96" s="5">
         <v>8</v>
@@ -3749,7 +3990,7 @@
         <v xml:space="preserve">  c_spi_vib_lc_line_refle = 147;</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.2">
@@ -3757,7 +3998,7 @@
         <v>148</v>
       </c>
       <c r="C97" s="23" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D97" s="5">
         <v>8</v>
@@ -3771,7 +4012,7 @@
         <v xml:space="preserve">  c_spi_vib_lc_line_cutoff = 148;</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.2">
@@ -3779,7 +4020,7 @@
         <v>149</v>
       </c>
       <c r="C98" s="23" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D98" s="5">
         <v>8</v>
@@ -3793,7 +4034,7 @@
         <v xml:space="preserve">  c_spi_vib_phaselk_shelv = 149;</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.2">
@@ -3815,7 +4056,7 @@
         <v xml:space="preserve">  c_spi_vib_gearing = 150;</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.2">
@@ -3823,7 +4064,7 @@
         <v>151</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D100" s="5">
         <v>8</v>
@@ -3837,7 +4078,7 @@
         <v xml:space="preserve">  c_spi_vib_dry_lvl = 151;</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.2">
@@ -3845,7 +4086,7 @@
         <v>152</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D101" s="5">
         <v>8</v>
@@ -3859,7 +4100,7 @@
         <v xml:space="preserve">  c_spi_vib_wet_lvl = 152;</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.2">
@@ -3867,7 +4108,7 @@
         <v>153</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D102" s="5">
         <v>8</v>
@@ -3881,7 +4122,7 @@
         <v xml:space="preserve">  c_spi_vib_flutter = 153;</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.2">
@@ -3889,7 +4130,7 @@
         <v>154</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D103" s="5">
         <v>8</v>
@@ -3903,7 +4144,7 @@
         <v xml:space="preserve">  c_spi_vib_premph_frequ = 154;</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.2">
@@ -3911,7 +4152,7 @@
         <v>155</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D104" s="5">
         <v>8</v>
@@ -3971,7 +4212,7 @@
         <v xml:space="preserve">  c_spi_lc_line_dly_0 = 160;</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.2">
@@ -4131,7 +4372,7 @@
         <v>169</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D118" s="5">
         <v>8</v>
@@ -4150,7 +4391,7 @@
         <v>170</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D119" s="5">
         <v>8</v>
@@ -4169,7 +4410,7 @@
         <v>171</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D120" s="5">
         <v>8</v>
@@ -4188,7 +4429,7 @@
         <v>172</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D121" s="5">
         <v>8</v>
@@ -4207,7 +4448,7 @@
         <v>173</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D122" s="5">
         <v>8</v>
@@ -4226,7 +4467,7 @@
         <v>174</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D123" s="5">
         <v>8</v>
@@ -4259,7 +4500,7 @@
       <c r="E125" s="17"/>
       <c r="F125" s="21"/>
       <c r="G125" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.2">
@@ -4319,7 +4560,7 @@
         <v xml:space="preserve">  c_spi_not_used = 179;</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
@@ -4549,7 +4790,7 @@
         <v>192</v>
       </c>
       <c r="C141" s="13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D141" s="5">
         <v>8</v>
@@ -4571,7 +4812,7 @@
         <v>193</v>
       </c>
       <c r="C142" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D142" s="5">
         <v>8</v>
@@ -4590,7 +4831,7 @@
         <v>194</v>
       </c>
       <c r="C143" s="13" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D143" s="5">
         <v>8</v>
@@ -4609,7 +4850,7 @@
         <v>195</v>
       </c>
       <c r="C144" s="24" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D144" s="5">
         <v>8</v>
@@ -4628,7 +4869,7 @@
         <v>196</v>
       </c>
       <c r="C145" s="24" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D145" s="5">
         <v>8</v>
@@ -4647,7 +4888,7 @@
         <v>197</v>
       </c>
       <c r="C146" s="13" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D146" s="5">
         <v>8</v>
@@ -4666,7 +4907,7 @@
         <v>198</v>
       </c>
       <c r="C147" s="24" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D147" s="5">
         <v>8</v>
@@ -4685,7 +4926,7 @@
         <v>199</v>
       </c>
       <c r="C148" s="13" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D148" s="5">
         <v>8</v>
@@ -4704,7 +4945,7 @@
         <v>200</v>
       </c>
       <c r="C149" s="24" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D149" s="5">
         <v>8</v>
@@ -4827,7 +5068,7 @@
         <v>224</v>
       </c>
       <c r="C159" s="24" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D159" s="5">
         <v>8</v>
@@ -4841,7 +5082,7 @@
         <v xml:space="preserve">  c_spi_lfo_phase_offset_horn_main_l = 224;</v>
       </c>
       <c r="G159" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.2">
@@ -4849,7 +5090,7 @@
         <v>225</v>
       </c>
       <c r="C160" s="24" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D160" s="5">
         <v>8</v>
@@ -4868,7 +5109,7 @@
         <v>226</v>
       </c>
       <c r="C161" s="24" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D161" s="5">
         <v>8</v>
@@ -4887,7 +5128,7 @@
         <v>227</v>
       </c>
       <c r="C162" s="24" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D162" s="5">
         <v>8</v>
@@ -4906,7 +5147,7 @@
         <v>228</v>
       </c>
       <c r="C163" s="24" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D163" s="5">
         <v>8</v>
@@ -4925,7 +5166,7 @@
         <v>229</v>
       </c>
       <c r="C164" s="24" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D164" s="5">
         <v>8</v>
@@ -4944,7 +5185,7 @@
         <v>230</v>
       </c>
       <c r="C165" s="13" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D165" s="5">
         <v>8</v>
@@ -4963,7 +5204,7 @@
         <v>231</v>
       </c>
       <c r="C166" s="24" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D166" s="5">
         <v>8</v>
@@ -5142,7 +5383,7 @@
         <v xml:space="preserve">  c_spi_dna_0 = 242;</v>
       </c>
       <c r="G177" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.2">
@@ -5164,7 +5405,7 @@
         <v xml:space="preserve">  c_spi_dna_1 = 243;</v>
       </c>
       <c r="G178" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.2">
@@ -5186,7 +5427,7 @@
         <v xml:space="preserve">  c_spi_lic_valid = 244;</v>
       </c>
       <c r="G179" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.2">
@@ -5200,7 +5441,7 @@
         <v>246</v>
       </c>
       <c r="C181" s="15" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D181" s="5">
         <v>32</v>
@@ -5214,7 +5455,7 @@
         <v xml:space="preserve">  c_spi_sam_command = 246;</v>
       </c>
       <c r="G181" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.2">
@@ -5222,7 +5463,7 @@
         <v>247</v>
       </c>
       <c r="G182" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/docs/HX3_FPGA_SPI.xlsx
+++ b/docs/HX3_FPGA_SPI.xlsx
@@ -69,9 +69,6 @@
     <t>FIFO TX Status</t>
   </si>
   <si>
-    <t>FIFO für Sendedaten MCU an FPGA</t>
-  </si>
-  <si>
     <t>SAM D1 Status</t>
   </si>
   <si>
@@ -321,9 +318,6 @@
     <t>PED TO BYPASS AMP</t>
   </si>
   <si>
-    <t>AO28  LOUDN BASS</t>
-  </si>
-  <si>
     <t>AO28 MIDRANGE</t>
   </si>
   <si>
@@ -844,6 +838,12 @@
   </si>
   <si>
     <t>XC6S25 Binary, 196 Blöcke</t>
+  </si>
+  <si>
+    <t>Füllstatus FIFO für Sendedaten MCU an FPGA</t>
+  </si>
+  <si>
+    <t>AO28 LOUDN BASS</t>
   </si>
 </sst>
 </file>
@@ -1396,10 +1396,10 @@
       <c r="E1" s="18"/>
       <c r="F1" s="18"/>
       <c r="L1" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:18" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
@@ -1416,19 +1416,19 @@
         <v>7</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>7</v>
@@ -1456,22 +1456,22 @@
         <v xml:space="preserve">  c_spi_fifo_tx_status = 0;</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>16</v>
+        <v>273</v>
       </c>
       <c r="L3" s="5">
         <v>0</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="N3" s="5">
         <v>32</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q3" s="17" t="str">
         <f>CONCATENATE("#define LCTARGET_",UPPER(SUBSTITUTE(O3," ","_"))," ",L3,"  // ",P3)</f>
@@ -1487,7 +1487,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D4" s="5">
         <v>32</v>
@@ -1501,22 +1501,22 @@
         <v xml:space="preserve">  c_spi_sam_d1_status = 1;</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L4" s="5">
         <v>1</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="N4" s="5">
         <v>32</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q4" s="17" t="str">
         <f t="shared" ref="Q4:Q16" si="2">CONCATENATE("#define LCTARGET_",UPPER(SUBSTITUTE(O4," ","_"))," ",L4,"  // ",P4)</f>
@@ -1532,7 +1532,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" s="5">
         <v>32</v>
@@ -1546,22 +1546,22 @@
         <v xml:space="preserve">  c_spi_midi_rx_data = 2;</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L5" s="5">
         <v>2</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="N5" s="5">
         <v>32</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q5" s="17" t="str">
         <f t="shared" si="2"/>
@@ -1577,7 +1577,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6" s="5">
         <v>32</v>
@@ -1600,10 +1600,10 @@
         <v>8</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="Q6" s="17" t="str">
         <f t="shared" si="2"/>
@@ -1619,7 +1619,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" s="11"/>
       <c r="D7" s="5">
@@ -1634,22 +1634,22 @@
         <v xml:space="preserve">  c_spi_throb_pos = 4;</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L7" s="5">
         <v>4</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="N7" s="5">
         <v>16</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q7" s="17" t="str">
         <f t="shared" si="2"/>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D8" s="5">
         <v>8</v>
@@ -1680,22 +1680,22 @@
         <v xml:space="preserve">  c_spi_scan_midich = 4;</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L8" s="5">
         <v>5</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="N8" s="5">
         <v>16</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="Q8" s="17" t="str">
         <f t="shared" si="2"/>
@@ -1711,7 +1711,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D9" s="5">
         <v>8</v>
@@ -1728,16 +1728,16 @@
         <v>6</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N9" s="5">
         <v>16</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="Q9" s="17" t="str">
         <f t="shared" si="2"/>
@@ -1753,7 +1753,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D10" s="5">
         <v>8</v>
@@ -1767,22 +1767,22 @@
         <v xml:space="preserve">  c_spi_scan_splitmode = 6;</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="L10" s="5">
         <v>7</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="N10" s="5">
         <v>16</v>
       </c>
       <c r="O10" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="Q10" s="17" t="str">
         <f t="shared" si="2"/>
@@ -1798,7 +1798,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D11" s="5">
         <v>8</v>
@@ -1824,7 +1824,7 @@
         <v>1</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="Q11" s="17" t="str">
         <f t="shared" si="2"/>
@@ -1840,7 +1840,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D12" s="5">
         <v>8</v>
@@ -1854,7 +1854,7 @@
         <v xml:space="preserve">  c_spi_scan_splitpoint = 8;</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L12" s="5">
         <v>9</v>
@@ -1869,7 +1869,7 @@
         <v>2</v>
       </c>
       <c r="P12" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="Q12" s="17" t="str">
         <f t="shared" si="2"/>
@@ -1885,7 +1885,7 @@
         <v>9</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D13" s="5">
         <v>8</v>
@@ -1899,7 +1899,7 @@
         <v xml:space="preserve">  c_spi_scan_click = 9;</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="L13" s="5">
         <v>10</v>
@@ -1914,7 +1914,7 @@
         <v>3</v>
       </c>
       <c r="P13" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="Q13" s="17" t="str">
         <f t="shared" si="2"/>
@@ -1930,7 +1930,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D14" s="5">
         <v>8</v>
@@ -1944,22 +1944,22 @@
         <v xml:space="preserve">  c_spi_scan_key_transpose = 10;</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="L14" s="5">
         <v>11</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="N14" s="5">
         <v>16</v>
       </c>
       <c r="O14" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="P14" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="Q14" s="17" t="str">
         <f t="shared" si="2"/>
@@ -1975,7 +1975,7 @@
         <v>11</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D15" s="5">
         <v>8</v>
@@ -1989,22 +1989,22 @@
         <v xml:space="preserve">  c_spi_scan_config_1 = 11;</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L15" s="5">
         <v>12</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="N15" s="5">
         <v>16</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="P15" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="Q15" s="17" t="str">
         <f t="shared" si="2"/>
@@ -2020,7 +2020,7 @@
         <v>12</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D16" s="5">
         <v>8</v>
@@ -2034,22 +2034,22 @@
         <v xml:space="preserve">  c_spi_scan_gen_transpose = 12;</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="L16" s="5">
         <v>13</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="N16" s="5">
         <v>16</v>
       </c>
       <c r="O16" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="P16" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="Q16" s="17" t="str">
         <f t="shared" si="2"/>
@@ -2065,7 +2065,7 @@
         <v>13</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D17" s="5">
         <v>8</v>
@@ -2082,7 +2082,7 @@
         <v>14</v>
       </c>
       <c r="O17" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
@@ -2090,7 +2090,7 @@
         <v>14</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D18" s="5">
         <v>8</v>
@@ -2104,13 +2104,13 @@
         <v xml:space="preserve">  c_spi_scan_pwm_localdisables = 14;</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L18" s="5">
         <v>15</v>
       </c>
       <c r="O18" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.2">
@@ -2118,7 +2118,7 @@
         <v>15</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D19" s="5">
         <v>8</v>
@@ -2132,7 +2132,7 @@
         <v xml:space="preserve">  c_spi_scan_pwm_auxport_leds = 15;</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="15" x14ac:dyDescent="0.25">
@@ -2140,15 +2140,15 @@
         <v>16</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="15" x14ac:dyDescent="0.25">
       <c r="L21" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="N21" s="1" t="s">
         <v>7</v>
@@ -2168,10 +2168,10 @@
         <v>8</v>
       </c>
       <c r="O22" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="P22" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="Q22" s="17" t="str">
         <f>CONCATENATE("#define BLOCK_",UPPER(SUBSTITUTE(O22," ","_"))," ",L22,"  // ",P22)</f>
@@ -2193,10 +2193,10 @@
         <v>8</v>
       </c>
       <c r="O23" s="5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="P23" s="5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="Q23" s="17" t="str">
         <f t="shared" ref="Q23:Q50" si="6">CONCATENATE("#define BLOCK_",UPPER(SUBSTITUTE(O23," ","_"))," ",L23,"  // ",P23)</f>
@@ -2212,7 +2212,7 @@
         <v>32</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D24" s="5">
         <v>16</v>
@@ -2229,10 +2229,10 @@
         <v>637</v>
       </c>
       <c r="O24" s="5" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="P24" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="Q24" s="17" t="str">
         <f t="shared" si="6"/>
@@ -2248,7 +2248,7 @@
         <v>33</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D25" s="5">
         <v>16</v>
@@ -2265,7 +2265,7 @@
         <v>639</v>
       </c>
       <c r="O25" s="5" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="Q25" s="17" t="str">
         <f t="shared" si="6"/>
@@ -2281,7 +2281,7 @@
         <v>34</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D26" s="5">
         <v>16</v>
@@ -2295,16 +2295,16 @@
         <v xml:space="preserve">  c_spi_upper_wet_lvl = 34;</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L26" s="5">
         <v>768</v>
       </c>
       <c r="O26" s="5" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P26" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="Q26" s="17" t="str">
         <f t="shared" si="6"/>
@@ -2320,7 +2320,7 @@
         <v>35</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D27" s="5">
         <v>16</v>
@@ -2337,10 +2337,10 @@
         <v>784</v>
       </c>
       <c r="O27" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P27" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="Q27" s="17" t="str">
         <f t="shared" si="6"/>
@@ -2356,7 +2356,7 @@
         <v>36</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D28" s="5">
         <v>16</v>
@@ -2373,10 +2373,10 @@
         <v>800</v>
       </c>
       <c r="O28" s="5" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="P28" s="5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="Q28" s="17" t="str">
         <f t="shared" si="6"/>
@@ -2392,7 +2392,7 @@
         <v>37</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D29" s="5">
         <v>16</v>
@@ -2406,16 +2406,16 @@
         <v xml:space="preserve">  c_spi_upper_dry_lvl = 37;</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L29" s="5">
         <v>928</v>
       </c>
       <c r="O29" s="5" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="P29" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="Q29" s="17" t="str">
         <f t="shared" si="6"/>
@@ -2431,7 +2431,7 @@
         <v>38</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D30" s="5">
         <v>16</v>
@@ -2451,7 +2451,7 @@
         <v>32</v>
       </c>
       <c r="O30" s="5" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="Q30" s="17" t="str">
         <f t="shared" si="6"/>
@@ -2467,7 +2467,7 @@
         <v>39</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D31" s="5">
         <v>16</v>
@@ -2484,13 +2484,13 @@
         <v>944</v>
       </c>
       <c r="M31" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="N31" s="5">
         <v>32</v>
       </c>
       <c r="O31" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="Q31" s="17" t="str">
         <f t="shared" si="6"/>
@@ -2506,7 +2506,7 @@
         <v>40</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D32" s="5">
         <v>16</v>
@@ -2520,7 +2520,7 @@
         <v xml:space="preserve">  c_spi_upper_bb_mech_cont_ena = 40;</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L32" s="5">
         <f>L31+2</f>
@@ -2533,7 +2533,7 @@
         <v>8</v>
       </c>
       <c r="O32" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Q32" s="17" t="str">
         <f t="shared" si="6"/>
@@ -2549,7 +2549,7 @@
         <v>41</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D33" s="5">
         <v>16</v>
@@ -2563,7 +2563,7 @@
         <v xml:space="preserve">  c_spi_upper_bb_adsr_ena = 41;</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L33" s="5">
         <f>L30+3</f>
@@ -2576,10 +2576,10 @@
         <v>8</v>
       </c>
       <c r="O33" s="5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P33" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="Q33" s="17" t="str">
         <f t="shared" si="6"/>
@@ -2595,7 +2595,7 @@
         <v>42</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D34" s="5">
         <v>16</v>
@@ -2609,7 +2609,7 @@
         <v xml:space="preserve">  c_spi_upper_bb_harp_sust_ena = 42;</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L34" s="5">
         <v>953</v>
@@ -2621,7 +2621,7 @@
         <v>8</v>
       </c>
       <c r="O34" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="Q34" s="17" t="str">
         <f t="shared" si="6"/>
@@ -2637,7 +2637,7 @@
         <v>43</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D35" s="5">
         <v>16</v>
@@ -2651,7 +2651,7 @@
         <v xml:space="preserve">  c_spi_upper_bb_to_dry_ena = 43;</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="L35" s="5">
         <f>L30+11</f>
@@ -2661,10 +2661,10 @@
         <v>32</v>
       </c>
       <c r="O35" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P35" s="5" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="Q35" s="17" t="str">
         <f t="shared" si="6"/>
@@ -2680,7 +2680,7 @@
         <v>44</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D36" s="5">
         <v>16</v>
@@ -2694,20 +2694,20 @@
         <v xml:space="preserve">  c_spi_lower_bb_adsr_ena = 44;</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L36" s="5">
         <f>L31+11</f>
         <v>955</v>
       </c>
       <c r="M36" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N36" s="5">
         <v>32</v>
       </c>
       <c r="O36" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="Q36" s="17" t="str">
         <f t="shared" si="6"/>
@@ -2723,7 +2723,7 @@
         <v>45</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D37" s="5">
         <v>16</v>
@@ -2737,20 +2737,20 @@
         <v xml:space="preserve">  c_spi_ped_to_vib_lvl = 45;</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="L37" s="5">
         <f>L36+1</f>
         <v>956</v>
       </c>
       <c r="M37" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N37" s="5">
         <v>32</v>
       </c>
       <c r="O37" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="Q37" s="17" t="str">
         <f t="shared" si="6"/>
@@ -2766,7 +2766,7 @@
         <v>46</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D38" s="5">
         <v>16</v>
@@ -2780,20 +2780,20 @@
         <v xml:space="preserve">  c_spi_ped_to_ao28_lvl = 46;</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L38" s="5">
         <f t="shared" ref="L38:L39" si="10">L37+1</f>
         <v>957</v>
       </c>
       <c r="M38" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N38" s="5">
         <v>32</v>
       </c>
       <c r="O38" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="Q38" s="17" t="str">
         <f t="shared" si="6"/>
@@ -2809,7 +2809,7 @@
         <v>47</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D39" s="5">
         <v>16</v>
@@ -2823,20 +2823,20 @@
         <v xml:space="preserve">  c_spi_ped_to_bypass_amp = 47;</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="L39" s="5">
         <f t="shared" si="10"/>
         <v>958</v>
       </c>
       <c r="M39" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N39" s="5">
         <v>32</v>
       </c>
       <c r="O39" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="Q39" s="17" t="str">
         <f t="shared" si="6"/>
@@ -2857,16 +2857,16 @@
         <v>959</v>
       </c>
       <c r="M40" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="N40" s="5">
         <v>16</v>
       </c>
       <c r="O40" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="P40" s="5" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="Q40" s="17" t="str">
         <f t="shared" si="6"/>
@@ -2886,10 +2886,10 @@
         <v>16</v>
       </c>
       <c r="O41" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="P41" s="5" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="Q41" s="17" t="str">
         <f t="shared" si="6"/>
@@ -2906,13 +2906,13 @@
         <v>960</v>
       </c>
       <c r="M42" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="N42" s="5">
         <v>16</v>
       </c>
       <c r="O42" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="Q42" s="17" t="str">
         <f t="shared" si="6"/>
@@ -2933,13 +2933,13 @@
         <v>964</v>
       </c>
       <c r="M43" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="N43" s="5">
         <v>16</v>
       </c>
       <c r="O43" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Q43" s="17" t="str">
         <f t="shared" si="6"/>
@@ -2955,7 +2955,7 @@
         <v>64</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D44" s="5">
         <v>8</v>
@@ -2969,20 +2969,20 @@
         <v xml:space="preserve">  c_spi_swap_dacs = 64;</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L44" s="5">
         <f t="shared" ref="L44:L49" si="12">L43+4</f>
         <v>968</v>
       </c>
       <c r="M44" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="N44" s="5">
         <v>16</v>
       </c>
       <c r="O44" s="5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="Q44" s="17" t="str">
         <f t="shared" si="6"/>
@@ -2998,7 +2998,7 @@
         <v>65</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D45" s="5">
         <v>8</v>
@@ -3012,20 +3012,20 @@
         <v xml:space="preserve">  c_spi_test_sel = 65;</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L45" s="5">
         <f t="shared" si="12"/>
         <v>972</v>
       </c>
       <c r="M45" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="N45" s="5">
         <v>16</v>
       </c>
       <c r="O45" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="Q45" s="17" t="str">
         <f t="shared" si="6"/>
@@ -3041,7 +3041,7 @@
         <v>66</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D46" s="16">
         <v>8</v>
@@ -3055,7 +3055,7 @@
         <v xml:space="preserve">  c_spi_inserts = 66;</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H46" s="16"/>
       <c r="I46" s="16"/>
@@ -3064,13 +3064,13 @@
         <v>976</v>
       </c>
       <c r="M46" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="N46" s="5">
         <v>16</v>
       </c>
       <c r="O46" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="Q46" s="17" t="str">
         <f t="shared" si="6"/>
@@ -3086,7 +3086,7 @@
         <v>67</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D47" s="5">
         <v>8</v>
@@ -3100,20 +3100,20 @@
         <v xml:space="preserve">  c_spi_leak_rndmask = 67;</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="L47" s="5">
         <f t="shared" si="12"/>
         <v>980</v>
       </c>
       <c r="M47" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="N47" s="5">
         <v>16</v>
       </c>
       <c r="O47" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="Q47" s="17" t="str">
         <f t="shared" si="6"/>
@@ -3129,7 +3129,7 @@
         <v>68</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D48" s="5">
         <v>8</v>
@@ -3143,20 +3143,20 @@
         <v xml:space="preserve">  c_spi_dds_tuning = 68;</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L48" s="5">
         <f t="shared" si="12"/>
         <v>984</v>
       </c>
       <c r="M48" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="N48" s="5">
         <v>16</v>
       </c>
       <c r="O48" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="Q48" s="17" t="str">
         <f t="shared" si="6"/>
@@ -3172,7 +3172,7 @@
         <v>69</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D49" s="5">
         <v>8</v>
@@ -3186,20 +3186,20 @@
         <v xml:space="preserve">  c_spi_amp_in_lvl = 69;</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L49" s="5">
         <f t="shared" si="12"/>
         <v>988</v>
       </c>
       <c r="M49" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="N49" s="5">
         <v>16</v>
       </c>
       <c r="O49" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Q49" s="17" t="str">
         <f t="shared" si="6"/>
@@ -3215,7 +3215,7 @@
         <v>70</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D50" s="5">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v xml:space="preserve">  c_spi_amp_out_lvl = 70;</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="L50" s="5">
         <v>992</v>
@@ -3241,10 +3241,10 @@
         <v>8</v>
       </c>
       <c r="O50" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="P50" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="Q50" s="17" t="str">
         <f t="shared" si="6"/>
@@ -3260,7 +3260,7 @@
         <v>71</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D51" s="5">
         <v>8</v>
@@ -3279,7 +3279,7 @@
         <v>72</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D52" s="5">
         <v>8</v>
@@ -3293,7 +3293,7 @@
         <v xml:space="preserve">  c_spi_master_volume = 72;</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.2">
@@ -3322,21 +3322,21 @@
         <v>80</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>100</v>
+        <v>274</v>
       </c>
       <c r="D57" s="5">
         <v>8</v>
       </c>
       <c r="E57" s="17" t="str">
         <f t="shared" ref="E57:E66" si="13">CONCATENATE("#define SPI_",UPPER(SUBSTITUTE(C57," ","_"))," ",A57)</f>
-        <v>#define SPI_AO28__LOUDN_BASS 80</v>
+        <v>#define SPI_AO28_LOUDN_BASS 80</v>
       </c>
       <c r="F57" s="21" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">  c_spi_ao28__loudn_bass = 80;</v>
+        <v xml:space="preserve">  c_spi_ao28_loudn_bass = 80;</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="Q57" s="17"/>
     </row>
@@ -3345,7 +3345,7 @@
         <v>81</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D58" s="5">
         <v>8</v>
@@ -3365,7 +3365,7 @@
         <v>82</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D59" s="5">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>83</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D60" s="5">
         <v>8</v>
@@ -3405,7 +3405,7 @@
         <v>84</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D61" s="5">
         <v>8</v>
@@ -3425,7 +3425,7 @@
         <v>85</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D62" s="5">
         <v>8</v>
@@ -3444,7 +3444,7 @@
         <v>86</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D63" s="5">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>87</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D64" s="5">
         <v>8</v>
@@ -3483,7 +3483,7 @@
         <v>88</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D65" s="5">
         <v>8</v>
@@ -3503,7 +3503,7 @@
         <v>89</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D66" s="5">
         <v>8</v>
@@ -3517,7 +3517,7 @@
         <v xml:space="preserve">  c_spi_ao28_bypass_sel = 89;</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Q66" s="17"/>
     </row>
@@ -3544,7 +3544,7 @@
         <v>112</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D71" s="5">
         <v>8</v>
@@ -3563,7 +3563,7 @@
         <v>113</v>
       </c>
       <c r="C72" s="22" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D72" s="5">
         <v>8</v>
@@ -3582,7 +3582,7 @@
         <v>114</v>
       </c>
       <c r="C73" s="22" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D73" s="5">
         <v>8</v>
@@ -3601,7 +3601,7 @@
         <v>115</v>
       </c>
       <c r="C74" s="22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D74" s="5">
         <v>8</v>
@@ -3620,7 +3620,7 @@
         <v>116</v>
       </c>
       <c r="C75" s="22" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D75" s="5">
         <v>8</v>
@@ -3639,7 +3639,7 @@
         <v>117</v>
       </c>
       <c r="C76" s="22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D76" s="5">
         <v>8</v>
@@ -3658,7 +3658,7 @@
         <v>118</v>
       </c>
       <c r="C77" s="22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D77" s="5">
         <v>8</v>
@@ -3677,7 +3677,7 @@
         <v>119</v>
       </c>
       <c r="C78" s="22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D78" s="5">
         <v>8</v>
@@ -3696,7 +3696,7 @@
         <v>120</v>
       </c>
       <c r="C79" s="22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D79" s="5">
         <v>8</v>
@@ -3715,7 +3715,7 @@
         <v>121</v>
       </c>
       <c r="C80" s="22" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D80" s="5">
         <v>8</v>
@@ -3734,7 +3734,7 @@
         <v>122</v>
       </c>
       <c r="C81" s="22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D81" s="5">
         <v>8</v>
@@ -3753,7 +3753,7 @@
         <v>123</v>
       </c>
       <c r="C82" s="22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D82" s="5">
         <v>8</v>
@@ -3772,7 +3772,7 @@
         <v>124</v>
       </c>
       <c r="C83" s="22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D83" s="5">
         <v>8</v>
@@ -3791,7 +3791,7 @@
         <v>125</v>
       </c>
       <c r="C84" s="22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D84" s="5">
         <v>8</v>
@@ -3810,7 +3810,7 @@
         <v>126</v>
       </c>
       <c r="C85" s="22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D85" s="5">
         <v>8</v>
@@ -3829,7 +3829,7 @@
         <v>127</v>
       </c>
       <c r="C86" s="22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D86" s="5">
         <v>8</v>
@@ -3862,7 +3862,7 @@
         <v xml:space="preserve">  c_spi_inc_loadcore = 128;</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
@@ -3884,7 +3884,7 @@
         <v xml:space="preserve">  c_spi_rst_loadcore = 129;</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
@@ -3910,7 +3910,7 @@
         <v>144</v>
       </c>
       <c r="C93" s="23" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D93" s="5">
         <v>8</v>
@@ -3924,7 +3924,7 @@
         <v xml:space="preserve">  c_spi_vib_preemph = 144;</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
@@ -3932,7 +3932,7 @@
         <v>145</v>
       </c>
       <c r="C94" s="23" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D94" s="5">
         <v>8</v>
@@ -3946,7 +3946,7 @@
         <v xml:space="preserve">  c_spi_vib_lc_line_age = 145;</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
@@ -3954,7 +3954,7 @@
         <v>146</v>
       </c>
       <c r="C95" s="23" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D95" s="5">
         <v>8</v>
@@ -3968,7 +3968,7 @@
         <v xml:space="preserve">  c_spi_vib_lc_line_fb = 146;</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
@@ -3976,7 +3976,7 @@
         <v>147</v>
       </c>
       <c r="C96" s="23" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D96" s="5">
         <v>8</v>
@@ -3990,7 +3990,7 @@
         <v xml:space="preserve">  c_spi_vib_lc_line_refle = 147;</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.2">
@@ -3998,7 +3998,7 @@
         <v>148</v>
       </c>
       <c r="C97" s="23" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D97" s="5">
         <v>8</v>
@@ -4012,7 +4012,7 @@
         <v xml:space="preserve">  c_spi_vib_lc_line_cutoff = 148;</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.2">
@@ -4020,7 +4020,7 @@
         <v>149</v>
       </c>
       <c r="C98" s="23" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D98" s="5">
         <v>8</v>
@@ -4034,7 +4034,7 @@
         <v xml:space="preserve">  c_spi_vib_phaselk_shelv = 149;</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.2">
@@ -4042,7 +4042,7 @@
         <v>150</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D99" s="5">
         <v>8</v>
@@ -4056,7 +4056,7 @@
         <v xml:space="preserve">  c_spi_vib_gearing = 150;</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.2">
@@ -4064,7 +4064,7 @@
         <v>151</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D100" s="5">
         <v>8</v>
@@ -4078,7 +4078,7 @@
         <v xml:space="preserve">  c_spi_vib_dry_lvl = 151;</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.2">
@@ -4086,7 +4086,7 @@
         <v>152</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D101" s="5">
         <v>8</v>
@@ -4100,7 +4100,7 @@
         <v xml:space="preserve">  c_spi_vib_wet_lvl = 152;</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.2">
@@ -4108,7 +4108,7 @@
         <v>153</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D102" s="5">
         <v>8</v>
@@ -4122,7 +4122,7 @@
         <v xml:space="preserve">  c_spi_vib_flutter = 153;</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.2">
@@ -4130,7 +4130,7 @@
         <v>154</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D103" s="5">
         <v>8</v>
@@ -4144,7 +4144,7 @@
         <v xml:space="preserve">  c_spi_vib_premph_frequ = 154;</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.2">
@@ -4152,7 +4152,7 @@
         <v>155</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D104" s="5">
         <v>8</v>
@@ -4166,7 +4166,7 @@
         <v xml:space="preserve">  c_spi_vib_modwave_phase = 155;</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.2">
@@ -4198,7 +4198,7 @@
         <v>160</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D109" s="5">
         <v>8</v>
@@ -4212,7 +4212,7 @@
         <v xml:space="preserve">  c_spi_lc_line_dly_0 = 160;</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.2">
@@ -4220,7 +4220,7 @@
         <v>161</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D110" s="5">
         <v>8</v>
@@ -4239,7 +4239,7 @@
         <v>162</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D111" s="5">
         <v>8</v>
@@ -4258,7 +4258,7 @@
         <v>163</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D112" s="5">
         <v>8</v>
@@ -4277,7 +4277,7 @@
         <v>164</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D113" s="5">
         <v>8</v>
@@ -4296,7 +4296,7 @@
         <v>165</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D114" s="5">
         <v>8</v>
@@ -4315,7 +4315,7 @@
         <v>166</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D115" s="5">
         <v>8</v>
@@ -4334,7 +4334,7 @@
         <v>167</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D116" s="5">
         <v>8</v>
@@ -4353,7 +4353,7 @@
         <v>168</v>
       </c>
       <c r="C117" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D117" s="5">
         <v>8</v>
@@ -4372,7 +4372,7 @@
         <v>169</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D118" s="5">
         <v>8</v>
@@ -4391,7 +4391,7 @@
         <v>170</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D119" s="5">
         <v>8</v>
@@ -4410,7 +4410,7 @@
         <v>171</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D120" s="5">
         <v>8</v>
@@ -4429,7 +4429,7 @@
         <v>172</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D121" s="5">
         <v>8</v>
@@ -4448,7 +4448,7 @@
         <v>173</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D122" s="5">
         <v>8</v>
@@ -4467,7 +4467,7 @@
         <v>174</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D123" s="5">
         <v>8</v>
@@ -4492,7 +4492,7 @@
         <v>176</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D125" s="5">
         <v>8</v>
@@ -4500,7 +4500,7 @@
       <c r="E125" s="17"/>
       <c r="F125" s="21"/>
       <c r="G125" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.2">
@@ -4508,7 +4508,7 @@
         <v>177</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D126" s="5">
         <v>8</v>
@@ -4527,7 +4527,7 @@
         <v>178</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D127" s="5">
         <v>8</v>
@@ -4546,7 +4546,7 @@
         <v>179</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D128" s="5">
         <v>8</v>
@@ -4560,7 +4560,7 @@
         <v xml:space="preserve">  c_spi_not_used = 179;</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
@@ -4568,7 +4568,7 @@
         <v>180</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D129" s="5">
         <v>8</v>
@@ -4587,7 +4587,7 @@
         <v>181</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D130" s="5">
         <v>8</v>
@@ -4606,7 +4606,7 @@
         <v>182</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D131" s="5">
         <v>8</v>
@@ -4625,7 +4625,7 @@
         <v>183</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D132" s="5">
         <v>8</v>
@@ -4644,7 +4644,7 @@
         <v>184</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D133" s="5">
         <v>8</v>
@@ -4663,7 +4663,7 @@
         <v>185</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D134" s="5">
         <v>8</v>
@@ -4682,7 +4682,7 @@
         <v>186</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D135" s="5">
         <v>8</v>
@@ -4695,7 +4695,7 @@
         <v>187</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D136" s="5">
         <v>8</v>
@@ -4714,7 +4714,7 @@
         <v>188</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D137" s="5">
         <v>8</v>
@@ -4733,7 +4733,7 @@
         <v>189</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D138" s="5">
         <v>8</v>
@@ -4752,7 +4752,7 @@
         <v>190</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D139" s="5">
         <v>8</v>
@@ -4771,7 +4771,7 @@
         <v>191</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D140" s="5">
         <v>8</v>
@@ -4790,7 +4790,7 @@
         <v>192</v>
       </c>
       <c r="C141" s="13" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D141" s="5">
         <v>8</v>
@@ -4804,7 +4804,7 @@
         <v xml:space="preserve">  c_spi_lfo_mod_horn_main_l = 192;</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
@@ -4812,7 +4812,7 @@
         <v>193</v>
       </c>
       <c r="C142" s="24" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D142" s="5">
         <v>8</v>
@@ -4831,7 +4831,7 @@
         <v>194</v>
       </c>
       <c r="C143" s="13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D143" s="5">
         <v>8</v>
@@ -4850,7 +4850,7 @@
         <v>195</v>
       </c>
       <c r="C144" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D144" s="5">
         <v>8</v>
@@ -4869,7 +4869,7 @@
         <v>196</v>
       </c>
       <c r="C145" s="24" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D145" s="5">
         <v>8</v>
@@ -4888,7 +4888,7 @@
         <v>197</v>
       </c>
       <c r="C146" s="13" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D146" s="5">
         <v>8</v>
@@ -4907,7 +4907,7 @@
         <v>198</v>
       </c>
       <c r="C147" s="24" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D147" s="5">
         <v>8</v>
@@ -4926,7 +4926,7 @@
         <v>199</v>
       </c>
       <c r="C148" s="13" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D148" s="5">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>200</v>
       </c>
       <c r="C149" s="24" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D149" s="5">
         <v>8</v>
@@ -4964,7 +4964,7 @@
         <v>201</v>
       </c>
       <c r="C150" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D150" s="5">
         <v>8</v>
@@ -4983,7 +4983,7 @@
         <v>202</v>
       </c>
       <c r="C151" s="13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D151" s="5">
         <v>8</v>
@@ -5002,7 +5002,7 @@
         <v>203</v>
       </c>
       <c r="C152" s="24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D152" s="5">
         <v>8</v>
@@ -5022,7 +5022,7 @@
         <v>204</v>
       </c>
       <c r="C153" s="25" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D153" s="5">
         <v>8</v>
@@ -5036,7 +5036,7 @@
         <v xml:space="preserve">  c_spi_horn_fir_filter_enable = 204;</v>
       </c>
       <c r="G153" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.2">
@@ -5068,7 +5068,7 @@
         <v>224</v>
       </c>
       <c r="C159" s="24" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D159" s="5">
         <v>8</v>
@@ -5082,7 +5082,7 @@
         <v xml:space="preserve">  c_spi_lfo_phase_offset_horn_main_l = 224;</v>
       </c>
       <c r="G159" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.2">
@@ -5090,7 +5090,7 @@
         <v>225</v>
       </c>
       <c r="C160" s="24" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D160" s="5">
         <v>8</v>
@@ -5109,7 +5109,7 @@
         <v>226</v>
       </c>
       <c r="C161" s="24" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D161" s="5">
         <v>8</v>
@@ -5128,7 +5128,7 @@
         <v>227</v>
       </c>
       <c r="C162" s="24" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D162" s="5">
         <v>8</v>
@@ -5147,7 +5147,7 @@
         <v>228</v>
       </c>
       <c r="C163" s="24" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D163" s="5">
         <v>8</v>
@@ -5166,7 +5166,7 @@
         <v>229</v>
       </c>
       <c r="C164" s="24" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D164" s="5">
         <v>8</v>
@@ -5185,7 +5185,7 @@
         <v>230</v>
       </c>
       <c r="C165" s="13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D165" s="5">
         <v>8</v>
@@ -5204,7 +5204,7 @@
         <v>231</v>
       </c>
       <c r="C166" s="24" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D166" s="5">
         <v>8</v>
@@ -5223,7 +5223,7 @@
         <v>232</v>
       </c>
       <c r="C167" s="24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D167" s="5">
         <v>8</v>
@@ -5242,7 +5242,7 @@
         <v>233</v>
       </c>
       <c r="C168" s="24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D168" s="5">
         <v>8</v>
@@ -5261,7 +5261,7 @@
         <v>234</v>
       </c>
       <c r="C169" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D169" s="5">
         <v>8</v>
@@ -5280,7 +5280,7 @@
         <v>235</v>
       </c>
       <c r="C170" s="24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D170" s="5">
         <v>8</v>
@@ -5369,7 +5369,7 @@
         <v>242</v>
       </c>
       <c r="B177" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D177" s="5">
         <v>32</v>
@@ -5383,7 +5383,7 @@
         <v xml:space="preserve">  c_spi_dna_0 = 242;</v>
       </c>
       <c r="G177" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.2">
@@ -5391,7 +5391,7 @@
         <v>243</v>
       </c>
       <c r="B178" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D178" s="5">
         <v>32</v>
@@ -5405,7 +5405,7 @@
         <v xml:space="preserve">  c_spi_dna_1 = 243;</v>
       </c>
       <c r="G178" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.2">
@@ -5413,7 +5413,7 @@
         <v>244</v>
       </c>
       <c r="B179" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D179" s="5">
         <v>32</v>
@@ -5427,7 +5427,7 @@
         <v xml:space="preserve">  c_spi_lic_valid = 244;</v>
       </c>
       <c r="G179" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.2">
@@ -5441,7 +5441,7 @@
         <v>246</v>
       </c>
       <c r="C181" s="15" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D181" s="5">
         <v>32</v>
@@ -5455,7 +5455,7 @@
         <v xml:space="preserve">  c_spi_sam_command = 246;</v>
       </c>
       <c r="G181" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.2">
@@ -5463,7 +5463,7 @@
         <v>247</v>
       </c>
       <c r="G182" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/docs/HX3_FPGA_SPI.xlsx
+++ b/docs/HX3_FPGA_SPI.xlsx
@@ -9,17 +9,18 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="360" yWindow="60" windowWidth="30915" windowHeight="16425"/>
+    <workbookView xWindow="360" yWindow="60" windowWidth="30915" windowHeight="16425" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="FPGA SPI" sheetId="3" r:id="rId1"/>
+    <sheet name="Tabelle1" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="306">
   <si>
     <t>Name</t>
   </si>
@@ -844,6 +845,99 @@
   </si>
   <si>
     <t>AO28 LOUDN BASS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  c_SystemInits</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Word = 496;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  c_VibKnobMode</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Word = c_SystemInits + 1; // #1497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  c_RestoreCommonPresetMask</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Word = c_SystemInits + 2; // #1498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  c_ButtonMask0</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Word = c_SystemInits + 3; // #1499 ALT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  c_ButtonMask1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Word = c_SystemInits + 4; // #1500 ALT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  c_ConfBits1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Word = c_SystemInits + 5; // #1501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  c_ConfBits2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Word = c_SystemInits + 6; // #1502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  c_ADCconfig</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Word = c_SystemInits + 7; // #1503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  c_1stDBselect</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Word = c_SystemInits + 8; // #1504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  c_2ndDBselect</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Word = c_SystemInits + 9; // #1505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  c_PedalDBsetup</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Word = c_SystemInits + 10; // #1506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  c_ADCscaling</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Word = c_SystemInits + 11; // #1507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  c_DeviceType</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Word = c_SystemInits + 13; // #1509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  c_PresetStructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Word = c_SystemInits + 14; // #1510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  c_EditMagicFlagIdx</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Word = c_SystemInits + 15; // #1511</t>
+  </si>
+  <si>
+    <t>C++# defines</t>
   </si>
 </sst>
 </file>
@@ -991,7 +1085,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1067,6 +1161,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5470,4 +5567,261 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="3" width="11.42578125" style="26"/>
+    <col min="4" max="4" width="20.140625" style="26" customWidth="1"/>
+    <col min="5" max="16384" width="11.42578125" style="26"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="26">
+        <v>496</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>275</v>
+      </c>
+      <c r="D2" s="26" t="str">
+        <f>UPPER(SUBSTITUTE(B2,"c_","OFS_"))</f>
+        <v xml:space="preserve">  OFS_SYSTEMINITS</v>
+      </c>
+      <c r="H2" s="26" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="26">
+        <v>497</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="D3" s="26" t="str">
+        <f t="shared" ref="D3:D17" si="0">UPPER(SUBSTITUTE(B3,"c_","OFS_"))</f>
+        <v xml:space="preserve">  OFS_VIBKNOBMODE</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="26">
+        <v>498</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>279</v>
+      </c>
+      <c r="D4" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  OFS_RESTORECOMMONPRESETMASK</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="26">
+        <v>499</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>281</v>
+      </c>
+      <c r="D5" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  OFS_BUTTONMASK0</v>
+      </c>
+      <c r="H5" s="26" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="26">
+        <v>500</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>283</v>
+      </c>
+      <c r="D6" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  OFS_BUTTONMASK1</v>
+      </c>
+      <c r="H6" s="26" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="26">
+        <v>501</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>285</v>
+      </c>
+      <c r="D7" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  OFS_CONFBITS1</v>
+      </c>
+      <c r="H7" s="26" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="26">
+        <v>502</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="D8" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  OFS_CONFBITS2</v>
+      </c>
+      <c r="H8" s="26" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="26">
+        <v>503</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>289</v>
+      </c>
+      <c r="D9" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  OFS_ADCCONFIG</v>
+      </c>
+      <c r="H9" s="26" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="26">
+        <v>504</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>291</v>
+      </c>
+      <c r="D10" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  OFS_1STDBSELECT</v>
+      </c>
+      <c r="H10" s="26" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="26">
+        <v>505</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>293</v>
+      </c>
+      <c r="D11" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  OFS_2NDDBSELECT</v>
+      </c>
+      <c r="H11" s="26" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="26">
+        <v>506</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="D12" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  OFS_PEDALDBSETUP</v>
+      </c>
+      <c r="H12" s="26" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="26">
+        <v>507</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="D13" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  OFS_ADCSCALING</v>
+      </c>
+      <c r="H13" s="26" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="26">
+        <v>508</v>
+      </c>
+      <c r="D14" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="26">
+        <v>509</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>299</v>
+      </c>
+      <c r="D15" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  OFS_DEVICETYPE</v>
+      </c>
+      <c r="H15" s="26" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="26">
+        <v>510</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>301</v>
+      </c>
+      <c r="D16" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  OFS_PRESETSTRUCTURE</v>
+      </c>
+      <c r="H16" s="26" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="26">
+        <v>511</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="D17" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  OFS_EDITMAGICFLAGIDX</v>
+      </c>
+      <c r="H17" s="26" t="s">
+        <v>304</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/HX3_FPGA_SPI.xlsx
+++ b/docs/HX3_FPGA_SPI.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="360" yWindow="60" windowWidth="30915" windowHeight="16425" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="60" windowWidth="30915" windowHeight="16425"/>
   </bookViews>
   <sheets>
     <sheet name="FPGA SPI" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="347">
   <si>
     <t>Name</t>
   </si>
@@ -847,97 +847,220 @@
     <t>AO28 LOUDN BASS</t>
   </si>
   <si>
-    <t xml:space="preserve">  c_SystemInits</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Word = 496;</t>
   </si>
   <si>
-    <t xml:space="preserve">  c_VibKnobMode</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Word = c_SystemInits + 1; // #1497</t>
   </si>
   <si>
-    <t xml:space="preserve">  c_RestoreCommonPresetMask</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Word = c_SystemInits + 2; // #1498</t>
   </si>
   <si>
-    <t xml:space="preserve">  c_ButtonMask0</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Word = c_SystemInits + 3; // #1499 ALT</t>
   </si>
   <si>
-    <t xml:space="preserve">  c_ButtonMask1</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Word = c_SystemInits + 4; // #1500 ALT</t>
   </si>
   <si>
-    <t xml:space="preserve">  c_ConfBits1</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Word = c_SystemInits + 5; // #1501</t>
   </si>
   <si>
-    <t xml:space="preserve">  c_ConfBits2</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Word = c_SystemInits + 6; // #1502</t>
   </si>
   <si>
-    <t xml:space="preserve">  c_ADCconfig</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Word = c_SystemInits + 7; // #1503</t>
   </si>
   <si>
-    <t xml:space="preserve">  c_1stDBselect</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Word = c_SystemInits + 8; // #1504</t>
   </si>
   <si>
-    <t xml:space="preserve">  c_2ndDBselect</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Word = c_SystemInits + 9; // #1505</t>
   </si>
   <si>
-    <t xml:space="preserve">  c_PedalDBsetup</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Word = c_SystemInits + 10; // #1506</t>
   </si>
   <si>
-    <t xml:space="preserve">  c_ADCscaling</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Word = c_SystemInits + 11; // #1507</t>
   </si>
   <si>
-    <t xml:space="preserve">  c_DeviceType</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Word = c_SystemInits + 13; // #1509</t>
   </si>
   <si>
-    <t xml:space="preserve">  c_PresetStructure</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Word = c_SystemInits + 14; // #1510</t>
   </si>
   <si>
-    <t xml:space="preserve">  c_EditMagicFlagIdx</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Word = c_SystemInits + 15; // #1511</t>
   </si>
   <si>
     <t>C++# defines</t>
+  </si>
+  <si>
+    <t>c_SystemInits</t>
+  </si>
+  <si>
+    <t>c_VibKnobMode</t>
+  </si>
+  <si>
+    <t>c_RestoreCommonPresetMask</t>
+  </si>
+  <si>
+    <t>c_ButtonMask0</t>
+  </si>
+  <si>
+    <t>c_ButtonMask1</t>
+  </si>
+  <si>
+    <t>c_ConfBits1</t>
+  </si>
+  <si>
+    <t>c_ConfBits2</t>
+  </si>
+  <si>
+    <t>c_ADCconfig</t>
+  </si>
+  <si>
+    <t>c_1stDBselect</t>
+  </si>
+  <si>
+    <t>c_2ndDBselect</t>
+  </si>
+  <si>
+    <t>c_PedalDBsetup</t>
+  </si>
+  <si>
+    <t>c_ADCscaling</t>
+  </si>
+  <si>
+    <t>c_DeviceType</t>
+  </si>
+  <si>
+    <t>c_PresetStructure</t>
+  </si>
+  <si>
+    <t>c_EditMagicFlagIdx</t>
+  </si>
+  <si>
+    <t>phases 0</t>
+  </si>
+  <si>
+    <t>phases 1</t>
+  </si>
+  <si>
+    <t>phases 2</t>
+  </si>
+  <si>
+    <t>phases 3</t>
+  </si>
+  <si>
+    <t>phases 4</t>
+  </si>
+  <si>
+    <t>phases 5</t>
+  </si>
+  <si>
+    <t>phases 6</t>
+  </si>
+  <si>
+    <t>phases 7</t>
+  </si>
+  <si>
+    <t>phases 8</t>
+  </si>
+  <si>
+    <t>phases 9</t>
+  </si>
+  <si>
+    <t>phases 10</t>
+  </si>
+  <si>
+    <t>phases 11</t>
+  </si>
+  <si>
+    <t>inits 0</t>
+  </si>
+  <si>
+    <t>inits 1</t>
+  </si>
+  <si>
+    <t>inits 2</t>
+  </si>
+  <si>
+    <t>inits 3</t>
+  </si>
+  <si>
+    <t>inits 4</t>
+  </si>
+  <si>
+    <t>inits 5</t>
+  </si>
+  <si>
+    <t>inits 6</t>
+  </si>
+  <si>
+    <t>inits 7</t>
+  </si>
+  <si>
+    <t>inits 8</t>
+  </si>
+  <si>
+    <t>inits 9</t>
+  </si>
+  <si>
+    <t>inits 10</t>
+  </si>
+  <si>
+    <t>inits 11</t>
+  </si>
+  <si>
+    <t>inits 12</t>
+  </si>
+  <si>
+    <t>inits 13</t>
+  </si>
+  <si>
+    <t>inits 14</t>
+  </si>
+  <si>
+    <t>inits 15</t>
+  </si>
+  <si>
+    <t>inits 16</t>
+  </si>
+  <si>
+    <t>inits 17</t>
+  </si>
+  <si>
+    <t>inits 18</t>
+  </si>
+  <si>
+    <t>inits 19</t>
+  </si>
+  <si>
+    <t>inits 20</t>
+  </si>
+  <si>
+    <t>inits 21</t>
+  </si>
+  <si>
+    <t>inits 22</t>
+  </si>
+  <si>
+    <t>inits 23</t>
+  </si>
+  <si>
+    <t>inits 24</t>
+  </si>
+  <si>
+    <t>inits 25</t>
+  </si>
+  <si>
+    <t>inits 26</t>
+  </si>
+  <si>
+    <t>inits 27</t>
+  </si>
+  <si>
+    <t>inits 28</t>
   </si>
 </sst>
 </file>
@@ -1011,7 +1134,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1072,6 +1195,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1085,7 +1214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1163,6 +1292,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1474,7 +1606,7 @@
   <cols>
     <col min="1" max="1" width="8.42578125" style="3" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" style="5" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="33.42578125" style="5" customWidth="1"/>
     <col min="4" max="4" width="11.42578125" style="5"/>
     <col min="5" max="5" width="36" style="5" customWidth="1"/>
     <col min="6" max="6" width="32.28515625" style="5" customWidth="1"/>
@@ -4369,7 +4501,7 @@
         <v xml:space="preserve">  c_spi_lc_line_dly_3 = 163;</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" s="3">
         <v>164</v>
       </c>
@@ -4388,7 +4520,7 @@
         <v xml:space="preserve">  c_spi_lc_line_dly_4 = 164;</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" s="3">
         <v>165</v>
       </c>
@@ -4407,7 +4539,7 @@
         <v xml:space="preserve">  c_spi_lc_line_dly_5 = 165;</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" s="3">
         <v>166</v>
       </c>
@@ -4426,7 +4558,7 @@
         <v xml:space="preserve">  c_spi_lc_line_dly_6 = 166;</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" s="3">
         <v>167</v>
       </c>
@@ -4445,7 +4577,7 @@
         <v xml:space="preserve">  c_spi_lc_line_dly_7 = 167;</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" s="3">
         <v>168</v>
       </c>
@@ -4464,7 +4596,7 @@
         <v xml:space="preserve">  c_spi_lc_line_dly_8 = 168;</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" s="3">
         <v>169</v>
       </c>
@@ -4483,7 +4615,7 @@
         <v xml:space="preserve">  c_spi_lc_line_dly_9 = 169;</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" s="3">
         <v>170</v>
       </c>
@@ -4502,7 +4634,7 @@
         <v xml:space="preserve">  c_spi_lc_line_dly_10 = 170;</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" s="3">
         <v>171</v>
       </c>
@@ -4521,7 +4653,7 @@
         <v xml:space="preserve">  c_spi_lc_line_dly_11 = 171;</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" s="3">
         <v>172</v>
       </c>
@@ -4540,7 +4672,7 @@
         <v xml:space="preserve">  c_spi_lc_line_dly_12 = 172;</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" s="3">
         <v>173</v>
       </c>
@@ -4559,7 +4691,7 @@
         <v xml:space="preserve">  c_spi_lc_line_dly_13 = 173;</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A123" s="3">
         <v>174</v>
       </c>
@@ -4578,13 +4710,13 @@
         <v xml:space="preserve">  c_spi_lc_line_dly_14 = 174;</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" s="3">
         <v>175</v>
       </c>
       <c r="F124" s="21"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" s="3">
         <v>176</v>
       </c>
@@ -4599,8 +4731,11 @@
       <c r="G125" s="5" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I125" s="5" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" s="3">
         <v>177</v>
       </c>
@@ -4618,8 +4753,11 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_speed_horn = 177;</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I126" s="5" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" s="3">
         <v>178</v>
       </c>
@@ -4637,8 +4775,11 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_speed_rotor = 178;</v>
       </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I127" s="5" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" s="3">
         <v>179</v>
       </c>
@@ -4659,8 +4800,11 @@
       <c r="G128" s="5" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I128" s="5" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A129" s="3">
         <v>180</v>
       </c>
@@ -4678,8 +4822,11 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_rotry_inp_lvl = 180;</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I129" s="5" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" s="3">
         <v>181</v>
       </c>
@@ -4697,8 +4844,11 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_rotry_horn_lvl = 181;</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I130" s="5" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" s="3">
         <v>182</v>
       </c>
@@ -4716,8 +4866,11 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_rotry_rotor_lvl = 182;</v>
       </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I131" s="5" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" s="3">
         <v>183</v>
       </c>
@@ -4735,8 +4888,11 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_rotry_horn_near_refl_lvl = 183;</v>
       </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I132" s="5" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" s="3">
         <v>184</v>
       </c>
@@ -4754,8 +4910,11 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_rotry_horn_room_refl_lvl = 184;</v>
       </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I133" s="5" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" s="3">
         <v>185</v>
       </c>
@@ -4773,8 +4932,11 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_rotry_xover_frequ = 185;</v>
       </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I134" s="5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" s="3">
         <v>186</v>
       </c>
@@ -4786,8 +4948,11 @@
       </c>
       <c r="E135" s="17"/>
       <c r="F135" s="21"/>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I135" s="5" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" s="3">
         <v>187</v>
       </c>
@@ -4805,8 +4970,11 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_rotry_pre_dly = 187;</v>
       </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I136" s="5" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" s="3">
         <v>188</v>
       </c>
@@ -4824,8 +4992,11 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_rotry_diffuse_1 = 188;</v>
       </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I137" s="5" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" s="3">
         <v>189</v>
       </c>
@@ -4843,8 +5014,11 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_rotry_diffuse_2 = 189;</v>
       </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I138" s="5" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" s="3">
         <v>190</v>
       </c>
@@ -4862,8 +5036,11 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_rotry_diffuse_3 = 190;</v>
       </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I139" s="5" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" s="3">
         <v>191</v>
       </c>
@@ -4881,8 +5058,11 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_rotry_diffuse_4 = 191;</v>
       </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I140" s="5" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141" s="3">
         <v>192</v>
       </c>
@@ -4903,8 +5083,11 @@
       <c r="G141" s="5" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I141" s="5" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A142" s="3">
         <v>193</v>
       </c>
@@ -4922,8 +5105,11 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lfo_mod_horn_main_r = 193;</v>
       </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I142" s="5" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A143" s="3">
         <v>194</v>
       </c>
@@ -4941,8 +5127,11 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lfo_mod_horn_refl_1_l_near = 194;</v>
       </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I143" s="5" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A144" s="3">
         <v>195</v>
       </c>
@@ -4960,8 +5149,11 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lfo_mod_horn_refl_1_r_near = 195;</v>
       </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I144" s="5" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" s="3">
         <v>196</v>
       </c>
@@ -4979,8 +5171,11 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lfo_mod_horn_refl_2_l_far = 196;</v>
       </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I145" s="5" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" s="3">
         <v>197</v>
       </c>
@@ -4998,8 +5193,11 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lfo_mod_horn_refl_2_r_far = 197;</v>
       </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I146" s="5" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" s="3">
         <v>198</v>
       </c>
@@ -5017,8 +5215,11 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lfo_mod_horn_throb_l = 198;</v>
       </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I147" s="5" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" s="3">
         <v>199</v>
       </c>
@@ -5036,8 +5237,11 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lfo_mod_horn_throb_r = 199;</v>
       </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I148" s="5" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" s="3">
         <v>200</v>
       </c>
@@ -5055,8 +5259,11 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lfo_mod_horn_cab = 200;</v>
       </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I149" s="5" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" s="3">
         <v>201</v>
       </c>
@@ -5074,8 +5281,11 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lfo_mod_rotor_main = 201;</v>
       </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I150" s="5" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" s="3">
         <v>202</v>
       </c>
@@ -5093,8 +5303,11 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lfo_mod_rotor_refl = 202;</v>
       </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I151" s="5" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A152" s="3">
         <v>203</v>
       </c>
@@ -5113,8 +5326,11 @@
         <v xml:space="preserve">  c_spi_lfo_mod_rotor_throb = 203;</v>
       </c>
       <c r="G152" s="10"/>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I152" s="5" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" s="3">
         <v>204</v>
       </c>
@@ -5135,32 +5351,35 @@
       <c r="G153" s="5" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I153" s="5" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A154" s="3">
         <v>205</v>
       </c>
       <c r="F154" s="21"/>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
       <c r="F155" s="21"/>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
       <c r="F156" s="21"/>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A157" s="3">
         <v>222</v>
       </c>
       <c r="F157" s="21"/>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A158" s="3">
         <v>223</v>
       </c>
       <c r="F158" s="21"/>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A159" s="3">
         <v>224</v>
       </c>
@@ -5181,8 +5400,11 @@
       <c r="G159" s="5" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I159" s="5" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A160" s="3">
         <v>225</v>
       </c>
@@ -5200,8 +5422,11 @@
         <f t="shared" si="18"/>
         <v xml:space="preserve">  c_spi_lfo_phase_offset_horn_main_r = 225;</v>
       </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I160" s="27" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" s="3">
         <v>226</v>
       </c>
@@ -5219,8 +5444,11 @@
         <f t="shared" si="18"/>
         <v xml:space="preserve">  c_spi_lfo_phase_offset_horn_refl_1_l_near_cab = 226;</v>
       </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I161" s="5" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" s="3">
         <v>227</v>
       </c>
@@ -5238,8 +5466,11 @@
         <f t="shared" si="18"/>
         <v xml:space="preserve">  c_spi_lfo_phase_offset_horn_refl_1_r_near_cab = 227;</v>
       </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I162" s="27" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A163" s="3">
         <v>228</v>
       </c>
@@ -5257,8 +5488,11 @@
         <f t="shared" si="18"/>
         <v xml:space="preserve">  c_spi_lfo_phase_offset_horn_refl_2_l__far = 228;</v>
       </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I163" s="5" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164" s="3">
         <v>229</v>
       </c>
@@ -5276,8 +5510,11 @@
         <f t="shared" si="18"/>
         <v xml:space="preserve">  c_spi_lfo_phase_offset_horn_refl_2_r_far = 229;</v>
       </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I164" s="27" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" s="3">
         <v>230</v>
       </c>
@@ -5295,8 +5532,11 @@
         <f t="shared" si="18"/>
         <v xml:space="preserve">  c_spi_lfo_phase_offset_horn_throb_l__2_khz = 230;</v>
       </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I165" s="5" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A166" s="3">
         <v>231</v>
       </c>
@@ -5314,8 +5554,11 @@
         <f t="shared" si="18"/>
         <v xml:space="preserve">  c_spi_lfo_phase_offset_horn_throb_r_2_khz = 231;</v>
       </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I166" s="27" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" s="3">
         <v>232</v>
       </c>
@@ -5333,8 +5576,11 @@
         <f t="shared" si="18"/>
         <v xml:space="preserve">  c_spi_lfo_phase_offset_horn_cab_4x = 232;</v>
       </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I167" s="5" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A168" s="3">
         <v>233</v>
       </c>
@@ -5352,8 +5598,11 @@
         <f t="shared" si="18"/>
         <v xml:space="preserve">  c_spi_lfo_phase_offset_rotor_main = 233;</v>
       </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I168" s="5" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A169" s="3">
         <v>234</v>
       </c>
@@ -5371,8 +5620,11 @@
         <f t="shared" si="18"/>
         <v xml:space="preserve">  c_spi_lfo_phase_offset_rotor_refl = 234;</v>
       </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I169" s="5" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A170" s="3">
         <v>235</v>
       </c>
@@ -5390,28 +5642,31 @@
         <f t="shared" si="18"/>
         <v xml:space="preserve">  c_spi_lfo_phase_offset_rotor_throb = 235;</v>
       </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I170" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A171" s="3">
         <v>236</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A172" s="3">
         <v>237</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A173" s="3">
         <v>238</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A174" s="3">
         <v>239</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A175" s="3">
         <v>240</v>
       </c>
@@ -5436,7 +5691,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A176" s="3">
         <v>241</v>
       </c>
@@ -5584,7 +5839,7 @@
         <v>164</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -5592,14 +5847,18 @@
         <v>496</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="D2" s="26" t="str">
         <f>UPPER(SUBSTITUTE(B2,"c_","OFS_"))</f>
-        <v xml:space="preserve">  OFS_SYSTEMINITS</v>
+        <v>OFS_SYSTEMINITS</v>
+      </c>
+      <c r="E2" s="26" t="str">
+        <f>CONCATENATE("#define ",D2," ",A2)</f>
+        <v>#define OFS_SYSTEMINITS 496</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -5607,14 +5866,18 @@
         <v>497</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="D3" s="26" t="str">
         <f t="shared" ref="D3:D17" si="0">UPPER(SUBSTITUTE(B3,"c_","OFS_"))</f>
-        <v xml:space="preserve">  OFS_VIBKNOBMODE</v>
+        <v>OFS_VIBKNOBMODE</v>
+      </c>
+      <c r="E3" s="26" t="str">
+        <f t="shared" ref="E3:E17" si="1">CONCATENATE("#define ",D3," ",A3)</f>
+        <v>#define OFS_VIBKNOBMODE 497</v>
       </c>
       <c r="H3" s="26" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -5622,14 +5885,18 @@
         <v>498</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="D4" s="26" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">  OFS_RESTORECOMMONPRESETMASK</v>
+        <v>OFS_RESTORECOMMONPRESETMASK</v>
+      </c>
+      <c r="E4" s="26" t="str">
+        <f t="shared" si="1"/>
+        <v>#define OFS_RESTORECOMMONPRESETMASK 498</v>
       </c>
       <c r="H4" s="26" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -5637,14 +5904,18 @@
         <v>499</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="D5" s="26" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">  OFS_BUTTONMASK0</v>
+        <v>OFS_BUTTONMASK0</v>
+      </c>
+      <c r="E5" s="26" t="str">
+        <f t="shared" si="1"/>
+        <v>#define OFS_BUTTONMASK0 499</v>
       </c>
       <c r="H5" s="26" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -5652,14 +5923,18 @@
         <v>500</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="D6" s="26" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">  OFS_BUTTONMASK1</v>
+        <v>OFS_BUTTONMASK1</v>
+      </c>
+      <c r="E6" s="26" t="str">
+        <f t="shared" si="1"/>
+        <v>#define OFS_BUTTONMASK1 500</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -5667,14 +5942,18 @@
         <v>501</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="D7" s="26" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">  OFS_CONFBITS1</v>
+        <v>OFS_CONFBITS1</v>
+      </c>
+      <c r="E7" s="26" t="str">
+        <f t="shared" si="1"/>
+        <v>#define OFS_CONFBITS1 501</v>
       </c>
       <c r="H7" s="26" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -5682,14 +5961,18 @@
         <v>502</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="D8" s="26" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">  OFS_CONFBITS2</v>
+        <v>OFS_CONFBITS2</v>
+      </c>
+      <c r="E8" s="26" t="str">
+        <f t="shared" si="1"/>
+        <v>#define OFS_CONFBITS2 502</v>
       </c>
       <c r="H8" s="26" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -5697,14 +5980,18 @@
         <v>503</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="D9" s="26" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">  OFS_ADCCONFIG</v>
+        <v>OFS_ADCCONFIG</v>
+      </c>
+      <c r="E9" s="26" t="str">
+        <f t="shared" si="1"/>
+        <v>#define OFS_ADCCONFIG 503</v>
       </c>
       <c r="H9" s="26" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -5712,14 +5999,18 @@
         <v>504</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="D10" s="26" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">  OFS_1STDBSELECT</v>
+        <v>OFS_1STDBSELECT</v>
+      </c>
+      <c r="E10" s="26" t="str">
+        <f t="shared" si="1"/>
+        <v>#define OFS_1STDBSELECT 504</v>
       </c>
       <c r="H10" s="26" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -5727,14 +6018,18 @@
         <v>505</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="D11" s="26" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">  OFS_2NDDBSELECT</v>
+        <v>OFS_2NDDBSELECT</v>
+      </c>
+      <c r="E11" s="26" t="str">
+        <f t="shared" si="1"/>
+        <v>#define OFS_2NDDBSELECT 505</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -5742,14 +6037,18 @@
         <v>506</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="D12" s="26" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">  OFS_PEDALDBSETUP</v>
+        <v>OFS_PEDALDBSETUP</v>
+      </c>
+      <c r="E12" s="26" t="str">
+        <f t="shared" si="1"/>
+        <v>#define OFS_PEDALDBSETUP 506</v>
       </c>
       <c r="H12" s="26" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -5757,14 +6056,18 @@
         <v>507</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="D13" s="26" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">  OFS_ADCSCALING</v>
+        <v>OFS_ADCSCALING</v>
+      </c>
+      <c r="E13" s="26" t="str">
+        <f t="shared" si="1"/>
+        <v>#define OFS_ADCSCALING 507</v>
       </c>
       <c r="H13" s="26" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -5781,14 +6084,18 @@
         <v>509</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="D15" s="26" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">  OFS_DEVICETYPE</v>
+        <v>OFS_DEVICETYPE</v>
+      </c>
+      <c r="E15" s="26" t="str">
+        <f t="shared" si="1"/>
+        <v>#define OFS_DEVICETYPE 509</v>
       </c>
       <c r="H15" s="26" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -5796,14 +6103,18 @@
         <v>510</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D16" s="26" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">  OFS_PRESETSTRUCTURE</v>
+        <v>OFS_PRESETSTRUCTURE</v>
+      </c>
+      <c r="E16" s="26" t="str">
+        <f t="shared" si="1"/>
+        <v>#define OFS_PRESETSTRUCTURE 510</v>
       </c>
       <c r="H16" s="26" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -5811,17 +6122,22 @@
         <v>511</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D17" s="26" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">  OFS_EDITMAGICFLAGIDX</v>
+        <v>OFS_EDITMAGICFLAGIDX</v>
+      </c>
+      <c r="E17" s="26" t="str">
+        <f t="shared" si="1"/>
+        <v>#define OFS_EDITMAGICFLAGIDX 511</v>
       </c>
       <c r="H17" s="26" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/HX3_FPGA_SPI.xlsx
+++ b/docs/HX3_FPGA_SPI.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="348">
   <si>
     <t>Name</t>
   </si>
@@ -1061,6 +1061,9 @@
   </si>
   <si>
     <t>inits 28</t>
+  </si>
+  <si>
+    <t>in liveCtrl berechnet</t>
   </si>
 </sst>
 </file>
@@ -4804,7 +4807,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129" s="3">
         <v>180</v>
       </c>
@@ -4826,7 +4829,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A130" s="3">
         <v>181</v>
       </c>
@@ -4848,7 +4851,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" s="3">
         <v>182</v>
       </c>
@@ -4870,7 +4873,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A132" s="3">
         <v>183</v>
       </c>
@@ -4892,7 +4895,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A133" s="3">
         <v>184</v>
       </c>
@@ -4914,7 +4917,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A134" s="3">
         <v>185</v>
       </c>
@@ -4936,7 +4939,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A135" s="3">
         <v>186</v>
       </c>
@@ -4952,7 +4955,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A136" s="3">
         <v>187</v>
       </c>
@@ -4974,7 +4977,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A137" s="3">
         <v>188</v>
       </c>
@@ -4996,7 +4999,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A138" s="3">
         <v>189</v>
       </c>
@@ -5018,7 +5021,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A139" s="3">
         <v>190</v>
       </c>
@@ -5040,7 +5043,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A140" s="3">
         <v>191</v>
       </c>
@@ -5062,7 +5065,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A141" s="3">
         <v>192</v>
       </c>
@@ -5087,7 +5090,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A142" s="3">
         <v>193</v>
       </c>
@@ -5105,11 +5108,14 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lfo_mod_horn_main_r = 193;</v>
       </c>
-      <c r="I142" s="5" t="s">
+      <c r="I142" s="27" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J142" s="5" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A143" s="3">
         <v>194</v>
       </c>
@@ -5131,7 +5137,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A144" s="3">
         <v>195</v>
       </c>
@@ -5149,11 +5155,14 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lfo_mod_horn_refl_1_r_near = 195;</v>
       </c>
-      <c r="I144" s="5" t="s">
+      <c r="I144" s="27" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J144" s="5" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A145" s="3">
         <v>196</v>
       </c>
@@ -5175,7 +5184,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A146" s="3">
         <v>197</v>
       </c>
@@ -5193,11 +5202,14 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lfo_mod_horn_refl_2_r_far = 197;</v>
       </c>
-      <c r="I146" s="5" t="s">
+      <c r="I146" s="27" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J146" s="5" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A147" s="3">
         <v>198</v>
       </c>
@@ -5219,7 +5231,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A148" s="3">
         <v>199</v>
       </c>
@@ -5237,11 +5249,14 @@
         <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lfo_mod_horn_throb_r = 199;</v>
       </c>
-      <c r="I148" s="5" t="s">
+      <c r="I148" s="27" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J148" s="5" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A149" s="3">
         <v>200</v>
       </c>
@@ -5263,7 +5278,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A150" s="3">
         <v>201</v>
       </c>
@@ -5285,7 +5300,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A151" s="3">
         <v>202</v>
       </c>
@@ -5307,7 +5322,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A152" s="3">
         <v>203</v>
       </c>
@@ -5330,7 +5345,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A153" s="3">
         <v>204</v>
       </c>
@@ -5355,31 +5370,31 @@
         <v>346</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A154" s="3">
         <v>205</v>
       </c>
       <c r="F154" s="21"/>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.2">
       <c r="F155" s="21"/>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.2">
       <c r="F156" s="21"/>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A157" s="3">
         <v>222</v>
       </c>
       <c r="F157" s="21"/>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A158" s="3">
         <v>223</v>
       </c>
       <c r="F158" s="21"/>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A159" s="3">
         <v>224</v>
       </c>
@@ -5404,7 +5419,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A160" s="3">
         <v>225</v>
       </c>
@@ -5425,8 +5440,11 @@
       <c r="I160" s="27" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J160" s="5" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A161" s="3">
         <v>226</v>
       </c>
@@ -5448,7 +5466,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A162" s="3">
         <v>227</v>
       </c>
@@ -5469,8 +5487,11 @@
       <c r="I162" s="27" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J162" s="5" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A163" s="3">
         <v>228</v>
       </c>
@@ -5492,7 +5513,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A164" s="3">
         <v>229</v>
       </c>
@@ -5513,8 +5534,11 @@
       <c r="I164" s="27" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J164" s="5" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A165" s="3">
         <v>230</v>
       </c>
@@ -5536,7 +5560,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A166" s="3">
         <v>231</v>
       </c>
@@ -5557,8 +5581,11 @@
       <c r="I166" s="27" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J166" s="5" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A167" s="3">
         <v>232</v>
       </c>
@@ -5580,7 +5607,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A168" s="3">
         <v>233</v>
       </c>
@@ -5602,7 +5629,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A169" s="3">
         <v>234</v>
       </c>
@@ -5624,7 +5651,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A170" s="3">
         <v>235</v>
       </c>
@@ -5646,27 +5673,27 @@
         <v>317</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A171" s="3">
         <v>236</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A172" s="3">
         <v>237</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A173" s="3">
         <v>238</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A174" s="3">
         <v>239</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A175" s="3">
         <v>240</v>
       </c>
@@ -5691,7 +5718,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A176" s="3">
         <v>241</v>
       </c>

--- a/docs/HX3_FPGA_SPI.xlsx
+++ b/docs/HX3_FPGA_SPI.xlsx
@@ -13,14 +13,14 @@
   </bookViews>
   <sheets>
     <sheet name="FPGA SPI" sheetId="3" r:id="rId1"/>
-    <sheet name="Tabelle1" sheetId="4" r:id="rId2"/>
+    <sheet name="System Inits" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="349">
   <si>
     <t>Name</t>
   </si>
@@ -1064,6 +1064,9 @@
   </si>
   <si>
     <t>in liveCtrl berechnet</t>
+  </si>
+  <si>
+    <t>DynSlope</t>
   </si>
 </sst>
 </file>
@@ -1710,8 +1713,8 @@
         <v>#define LCTARGET_SCAN_DRIVER 0  // aus DataFlash</v>
       </c>
       <c r="R3" s="21" t="str">
-        <f>CONCATENATE("  c_lctarget_",LOWER(SUBSTITUTE(O3," ","_"))," = ",L3,";")</f>
-        <v xml:space="preserve">  c_lctarget_scan_driver = 0;</v>
+        <f>CONCATENATE("  c_lc_",LOWER(SUBSTITUTE(O3," ","_")),": Byte = ",L3,";")</f>
+        <v xml:space="preserve">  c_lc_scan_driver: Byte = 0;</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
@@ -1755,8 +1758,8 @@
         <v>#define LCTARGET_TAPERING 1  // aus DataFlash</v>
       </c>
       <c r="R4" s="21" t="str">
-        <f t="shared" ref="R4:R16" si="3">CONCATENATE("  c_lctarget_",LOWER(SUBSTITUTE(O4," ","_"))," = ",L4,";")</f>
-        <v xml:space="preserve">  c_lctarget_tapering = 1;</v>
+        <f t="shared" ref="R4:R16" si="3">CONCATENATE("  c_lc_",LOWER(SUBSTITUTE(O4," ","_")),": Byte = ",L4,";")</f>
+        <v xml:space="preserve">  c_lc_tapering: Byte = 1;</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
@@ -1801,7 +1804,7 @@
       </c>
       <c r="R5" s="21" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">  c_lctarget_fir_coeff = 2;</v>
+        <v xml:space="preserve">  c_lc_fir_coeff: Byte = 2;</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
@@ -1843,7 +1846,7 @@
       </c>
       <c r="R6" s="21" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">  c_lctarget_keymap = 3;</v>
+        <v xml:space="preserve">  c_lc_keymap: Byte = 3;</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
@@ -1889,7 +1892,7 @@
       </c>
       <c r="R7" s="21" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">  c_lctarget_waveset = 4;</v>
+        <v xml:space="preserve">  c_lc_waveset: Byte = 4;</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
@@ -1935,7 +1938,7 @@
       </c>
       <c r="R8" s="21" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">  c_lctarget_tuning_vals = 5;</v>
+        <v xml:space="preserve">  c_lc_tuning_vals: Byte = 5;</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
@@ -1977,7 +1980,7 @@
       </c>
       <c r="R9" s="21" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">  c_lctarget_hp_filter = 6;</v>
+        <v xml:space="preserve">  c_lc_hp_filter: Byte = 6;</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
@@ -2022,7 +2025,7 @@
       </c>
       <c r="R10" s="21" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">  c_lctarget_tube_amp_slope = 7;</v>
+        <v xml:space="preserve">  c_lc_tube_amp_slope: Byte = 7;</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
@@ -2064,7 +2067,7 @@
       </c>
       <c r="R11" s="21" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">  c_lctarget_upper_drawbars = 8;</v>
+        <v xml:space="preserve">  c_lc_upper_drawbars: Byte = 8;</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
@@ -2109,7 +2112,7 @@
       </c>
       <c r="R12" s="21" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">  c_lctarget_lower_drawbars = 9;</v>
+        <v xml:space="preserve">  c_lc_lower_drawbars: Byte = 9;</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
@@ -2154,7 +2157,7 @@
       </c>
       <c r="R13" s="21" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">  c_lctarget_pedal_drawbars = 10;</v>
+        <v xml:space="preserve">  c_lc_pedal_drawbars: Byte = 10;</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
@@ -2199,7 +2202,7 @@
       </c>
       <c r="R14" s="21" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">  c_lctarget_adsr_upper = 11;</v>
+        <v xml:space="preserve">  c_lc_adsr_upper: Byte = 11;</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
@@ -2244,7 +2247,7 @@
       </c>
       <c r="R15" s="21" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">  c_lctarget_adsr_lower = 12;</v>
+        <v xml:space="preserve">  c_lc_adsr_lower: Byte = 12;</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
@@ -2289,7 +2292,7 @@
       </c>
       <c r="R16" s="21" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">  c_lctarget_adsr_pedal = 13;</v>
+        <v xml:space="preserve">  c_lc_adsr_pedal: Byte = 13;</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
@@ -2313,8 +2316,25 @@
       <c r="L17" s="5">
         <v>14</v>
       </c>
+      <c r="M17" s="5">
+        <v>256</v>
+      </c>
+      <c r="N17" s="5">
+        <v>8</v>
+      </c>
       <c r="O17" s="5" t="s">
-        <v>191</v>
+        <v>348</v>
+      </c>
+      <c r="P17" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q17" s="17" t="str">
+        <f t="shared" ref="Q17" si="6">CONCATENATE("#define LCTARGET_",UPPER(SUBSTITUTE(O17," ","_"))," ",L17,"  // ",P17)</f>
+        <v>#define LCTARGET_DYNSLOPE 14  // berechnet</v>
+      </c>
+      <c r="R17" s="21" t="str">
+        <f t="shared" ref="R17" si="7">CONCATENATE("  c_lc_",LOWER(SUBSTITUTE(O17," ","_")),": Byte = ",L17,";")</f>
+        <v xml:space="preserve">  c_lc_dynslope: Byte = 14;</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
@@ -2431,11 +2451,11 @@
         <v>266</v>
       </c>
       <c r="Q23" s="17" t="str">
-        <f t="shared" ref="Q23:Q50" si="6">CONCATENATE("#define BLOCK_",UPPER(SUBSTITUTE(O23," ","_"))," ",L23,"  // ",P23)</f>
+        <f t="shared" ref="Q23:Q50" si="8">CONCATENATE("#define BLOCK_",UPPER(SUBSTITUTE(O23," ","_"))," ",L23,"  // ",P23)</f>
         <v>#define BLOCK_FAILSAFE_BASE 320  // Sicherungskopie</v>
       </c>
       <c r="R23" s="21" t="str">
-        <f t="shared" ref="R23:R50" si="7">CONCATENATE("  c_",LOWER(SUBSTITUTE(O23," ","_")),": Word = ",L23,";  // ",P23)</f>
+        <f t="shared" ref="R23:R50" si="9">CONCATENATE("  c_",LOWER(SUBSTITUTE(O23," ","_")),": Word = ",L23,";  // ",P23)</f>
         <v xml:space="preserve">  c_failsafe_base: Word = 320;  // Sicherungskopie</v>
       </c>
     </row>
@@ -2450,11 +2470,11 @@
         <v>16</v>
       </c>
       <c r="E24" s="17" t="str">
-        <f t="shared" ref="E24:E39" si="8">CONCATENATE("#define SPI_",UPPER(SUBSTITUTE(C24," ","_"))," ",A24)</f>
+        <f t="shared" ref="E24:E39" si="10">CONCATENATE("#define SPI_",UPPER(SUBSTITUTE(C24," ","_"))," ",A24)</f>
         <v>#define SPI_PERC_ENA 32</v>
       </c>
       <c r="F24" s="21" t="str">
-        <f t="shared" ref="F24:F87" si="9">CONCATENATE("  c_spi_",LOWER(SUBSTITUTE(C24," ","_"))," = ",A24,";")</f>
+        <f t="shared" ref="F24:F87" si="11">CONCATENATE("  c_spi_",LOWER(SUBSTITUTE(C24," ","_"))," = ",A24,";")</f>
         <v xml:space="preserve">  c_spi_perc_ena = 32;</v>
       </c>
       <c r="L24" s="5">
@@ -2467,11 +2487,11 @@
         <v>267</v>
       </c>
       <c r="Q24" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>#define BLOCK_UPDATE_INFO 637  // Update List</v>
       </c>
       <c r="R24" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_update_info: Word = 637;  // Update List</v>
       </c>
     </row>
@@ -2486,11 +2506,11 @@
         <v>16</v>
       </c>
       <c r="E25" s="17" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>#define SPI_PERC_VOL 33</v>
       </c>
       <c r="F25" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_perc_vol = 33;</v>
       </c>
       <c r="L25" s="5">
@@ -2500,11 +2520,11 @@
         <v>259</v>
       </c>
       <c r="Q25" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">#define BLOCK_BOARD_INFO 639  // </v>
       </c>
       <c r="R25" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_board_info: Word = 639;  // </v>
       </c>
     </row>
@@ -2519,11 +2539,11 @@
         <v>16</v>
       </c>
       <c r="E26" s="17" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>#define SPI_UPPER_WET_LVL 34</v>
       </c>
       <c r="F26" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_upper_wet_lvl = 34;</v>
       </c>
       <c r="G26" s="5" t="s">
@@ -2539,11 +2559,11 @@
         <v>265</v>
       </c>
       <c r="Q26" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>#define BLOCK_SPEAKER_MODEL_BASE 768  // 16 Blöcke</v>
       </c>
       <c r="R26" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_speaker_model_base: Word = 768;  // 16 Blöcke</v>
       </c>
     </row>
@@ -2558,11 +2578,11 @@
         <v>16</v>
       </c>
       <c r="E27" s="17" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>#define SPI_LOWER_LVL 35</v>
       </c>
       <c r="F27" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_lower_lvl = 35;</v>
       </c>
       <c r="L27" s="5">
@@ -2575,11 +2595,11 @@
         <v>265</v>
       </c>
       <c r="Q27" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>#define BLOCK_ORGAN_MODEL_BASE 784  // 16 Blöcke</v>
       </c>
       <c r="R27" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_organ_model_base: Word = 784;  // 16 Blöcke</v>
       </c>
     </row>
@@ -2594,11 +2614,11 @@
         <v>16</v>
       </c>
       <c r="E28" s="17" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>#define SPI_PEDAL_LVL 36</v>
       </c>
       <c r="F28" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_pedal_lvl = 36;</v>
       </c>
       <c r="L28" s="5">
@@ -2611,11 +2631,11 @@
         <v>264</v>
       </c>
       <c r="Q28" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>#define BLOCK_PRESET_BASE 800  // 100 Blöcke</v>
       </c>
       <c r="R28" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_preset_base: Word = 800;  // 100 Blöcke</v>
       </c>
     </row>
@@ -2630,11 +2650,11 @@
         <v>16</v>
       </c>
       <c r="E29" s="17" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>#define SPI_UPPER_DRY_LVL 37</v>
       </c>
       <c r="F29" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_upper_dry_lvl = 37;</v>
       </c>
       <c r="G29" s="5" t="s">
@@ -2650,11 +2670,11 @@
         <v>265</v>
       </c>
       <c r="Q29" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>#define BLOCK_MIDI_CC_BASE 928  // 16 Blöcke</v>
       </c>
       <c r="R29" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_midi_cc_base: Word = 928;  // 16 Blöcke</v>
       </c>
     </row>
@@ -2669,11 +2689,11 @@
         <v>16</v>
       </c>
       <c r="E30" s="17" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>#define SPI_PERC_PRECHARGE_TIME 38</v>
       </c>
       <c r="F30" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_perc_precharge_time = 38;</v>
       </c>
       <c r="L30" s="5">
@@ -2686,11 +2706,11 @@
         <v>221</v>
       </c>
       <c r="Q30" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">#define BLOCK_CORE_BASE 944  // </v>
       </c>
       <c r="R30" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_core_base: Word = 944;  // </v>
       </c>
     </row>
@@ -2705,11 +2725,11 @@
         <v>16</v>
       </c>
       <c r="E31" s="17" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>#define SPI_PERC_DECAY_TIME 39</v>
       </c>
       <c r="F31" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_perc_decay_time = 39;</v>
       </c>
       <c r="L31" s="5">
@@ -2725,11 +2745,11 @@
         <v>222</v>
       </c>
       <c r="Q31" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">#define BLOCK_SCAN 944  // </v>
       </c>
       <c r="R31" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_scan: Word = 944;  // </v>
       </c>
     </row>
@@ -2744,11 +2764,11 @@
         <v>16</v>
       </c>
       <c r="E32" s="17" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>#define SPI_UPPER_BB_MECH_CONT_ENA 40</v>
       </c>
       <c r="F32" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_upper_bb_mech_cont_ena = 40;</v>
       </c>
       <c r="G32" s="5" t="s">
@@ -2768,11 +2788,11 @@
         <v>223</v>
       </c>
       <c r="Q32" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">#define BLOCK_VOICE 946  // </v>
       </c>
       <c r="R32" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_voice: Word = 946;  // </v>
       </c>
     </row>
@@ -2787,11 +2807,11 @@
         <v>16</v>
       </c>
       <c r="E33" s="17" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>#define SPI_UPPER_BB_ADSR_ENA 41</v>
       </c>
       <c r="F33" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_upper_bb_adsr_ena = 41;</v>
       </c>
       <c r="G33" s="5" t="s">
@@ -2814,11 +2834,11 @@
         <v>271</v>
       </c>
       <c r="Q33" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>#define BLOCK_DEFAULTS 947  // HX3 Edit Array</v>
       </c>
       <c r="R33" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_defaults: Word = 947;  // HX3 Edit Array</v>
       </c>
     </row>
@@ -2833,11 +2853,11 @@
         <v>16</v>
       </c>
       <c r="E34" s="17" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>#define SPI_UPPER_BB_HARP_SUST_ENA 42</v>
       </c>
       <c r="F34" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_upper_bb_harp_sust_ena = 42;</v>
       </c>
       <c r="G34" s="5" t="s">
@@ -2856,11 +2876,11 @@
         <v>225</v>
       </c>
       <c r="Q34" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">#define BLOCK_EEPROM 953  // </v>
       </c>
       <c r="R34" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_eeprom: Word = 953;  // </v>
       </c>
     </row>
@@ -2875,11 +2895,11 @@
         <v>16</v>
       </c>
       <c r="E35" s="17" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>#define SPI_UPPER_BB_TO_DRY_ENA 43</v>
       </c>
       <c r="F35" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_upper_bb_to_dry_ena = 43;</v>
       </c>
       <c r="G35" s="5" t="s">
@@ -2899,11 +2919,11 @@
         <v>270</v>
       </c>
       <c r="Q35" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>#define BLOCK_TAPER_BASE 955  // 4 Taperings</v>
       </c>
       <c r="R35" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_taper_base: Word = 955;  // 4 Taperings</v>
       </c>
     </row>
@@ -2918,11 +2938,11 @@
         <v>16</v>
       </c>
       <c r="E36" s="17" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>#define SPI_LOWER_BB_ADSR_ENA 44</v>
       </c>
       <c r="F36" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_lower_bb_adsr_ena = 44;</v>
       </c>
       <c r="G36" s="5" t="s">
@@ -2942,11 +2962,11 @@
         <v>209</v>
       </c>
       <c r="Q36" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">#define BLOCK_TAPER_0 955  // </v>
       </c>
       <c r="R36" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_taper_0: Word = 955;  // </v>
       </c>
     </row>
@@ -2961,11 +2981,11 @@
         <v>16</v>
       </c>
       <c r="E37" s="17" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>#define SPI_PED_TO_VIB_LVL 45</v>
       </c>
       <c r="F37" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_ped_to_vib_lvl = 45;</v>
       </c>
       <c r="G37" s="5" t="s">
@@ -2985,11 +3005,11 @@
         <v>210</v>
       </c>
       <c r="Q37" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">#define BLOCK_TAPER_1 956  // </v>
       </c>
       <c r="R37" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_taper_1: Word = 956;  // </v>
       </c>
     </row>
@@ -3004,18 +3024,18 @@
         <v>16</v>
       </c>
       <c r="E38" s="17" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>#define SPI_PED_TO_AO28_LVL 46</v>
       </c>
       <c r="F38" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_ped_to_ao28_lvl = 46;</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>147</v>
       </c>
       <c r="L38" s="5">
-        <f t="shared" ref="L38:L39" si="10">L37+1</f>
+        <f t="shared" ref="L38:L39" si="12">L37+1</f>
         <v>957</v>
       </c>
       <c r="M38" s="5" t="s">
@@ -3028,11 +3048,11 @@
         <v>211</v>
       </c>
       <c r="Q38" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">#define BLOCK_TAPER_2 957  // </v>
       </c>
       <c r="R38" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_taper_2: Word = 957;  // </v>
       </c>
     </row>
@@ -3047,18 +3067,18 @@
         <v>16</v>
       </c>
       <c r="E39" s="17" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>#define SPI_PED_TO_BYPASS_AMP 47</v>
       </c>
       <c r="F39" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_ped_to_bypass_amp = 47;</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>148</v>
       </c>
       <c r="L39" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>958</v>
       </c>
       <c r="M39" s="5" t="s">
@@ -3071,11 +3091,11 @@
         <v>212</v>
       </c>
       <c r="Q39" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">#define BLOCK_TAPER_3 958  // </v>
       </c>
       <c r="R39" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_taper_3: Word = 958;  // </v>
       </c>
     </row>
@@ -3101,11 +3121,11 @@
         <v>268</v>
       </c>
       <c r="Q40" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>#define BLOCK_FIR_COEFF 959  // Filterkoeffizienten</v>
       </c>
       <c r="R40" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_fir_coeff: Word = 959;  // Filterkoeffizienten</v>
       </c>
     </row>
@@ -3124,11 +3144,11 @@
         <v>269</v>
       </c>
       <c r="Q41" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>#define BLOCK_WAVESET_BASE 960  // 8 Wavesets</v>
       </c>
       <c r="R41" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_waveset_base: Word = 960;  // 8 Wavesets</v>
       </c>
     </row>
@@ -3147,11 +3167,11 @@
         <v>213</v>
       </c>
       <c r="Q42" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">#define BLOCK_WAVESET_0 960  // </v>
       </c>
       <c r="R42" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_waveset_0: Word = 960;  // </v>
       </c>
     </row>
@@ -3174,11 +3194,11 @@
         <v>214</v>
       </c>
       <c r="Q43" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">#define BLOCK_WAVESET_1 964  // </v>
       </c>
       <c r="R43" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_waveset_1: Word = 964;  // </v>
       </c>
     </row>
@@ -3193,18 +3213,18 @@
         <v>8</v>
       </c>
       <c r="E44" s="17" t="str">
-        <f t="shared" ref="E44:E52" si="11">CONCATENATE("#define SPI_",UPPER(SUBSTITUTE(C44," ","_"))," ",A44)</f>
+        <f t="shared" ref="E44:E52" si="13">CONCATENATE("#define SPI_",UPPER(SUBSTITUTE(C44," ","_"))," ",A44)</f>
         <v>#define SPI_SWAP_DACS 64</v>
       </c>
       <c r="F44" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_swap_dacs = 64;</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>141</v>
       </c>
       <c r="L44" s="5">
-        <f t="shared" ref="L44:L49" si="12">L43+4</f>
+        <f t="shared" ref="L44:L49" si="14">L43+4</f>
         <v>968</v>
       </c>
       <c r="M44" s="5" t="s">
@@ -3217,11 +3237,11 @@
         <v>215</v>
       </c>
       <c r="Q44" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">#define BLOCK_WAVESET_2 968  // </v>
       </c>
       <c r="R44" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_waveset_2: Word = 968;  // </v>
       </c>
     </row>
@@ -3236,18 +3256,18 @@
         <v>8</v>
       </c>
       <c r="E45" s="17" t="str">
+        <f t="shared" si="13"/>
+        <v>#define SPI_TEST_SEL 65</v>
+      </c>
+      <c r="F45" s="21" t="str">
         <f t="shared" si="11"/>
-        <v>#define SPI_TEST_SEL 65</v>
-      </c>
-      <c r="F45" s="21" t="str">
-        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_spi_test_sel = 65;</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>28</v>
       </c>
       <c r="L45" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>972</v>
       </c>
       <c r="M45" s="5" t="s">
@@ -3260,11 +3280,11 @@
         <v>216</v>
       </c>
       <c r="Q45" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">#define BLOCK_WAVESET_3 972  // </v>
       </c>
       <c r="R45" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_waveset_3: Word = 972;  // </v>
       </c>
     </row>
@@ -3279,11 +3299,11 @@
         <v>8</v>
       </c>
       <c r="E46" s="17" t="str">
+        <f t="shared" si="13"/>
+        <v>#define SPI_INSERTS 66</v>
+      </c>
+      <c r="F46" s="21" t="str">
         <f t="shared" si="11"/>
-        <v>#define SPI_INSERTS 66</v>
-      </c>
-      <c r="F46" s="21" t="str">
-        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_spi_inserts = 66;</v>
       </c>
       <c r="G46" s="16" t="s">
@@ -3292,7 +3312,7 @@
       <c r="H46" s="16"/>
       <c r="I46" s="16"/>
       <c r="L46" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>976</v>
       </c>
       <c r="M46" s="5" t="s">
@@ -3305,11 +3325,11 @@
         <v>217</v>
       </c>
       <c r="Q46" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">#define BLOCK_WAVESET_4 976  // </v>
       </c>
       <c r="R46" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_waveset_4: Word = 976;  // </v>
       </c>
     </row>
@@ -3324,18 +3344,18 @@
         <v>8</v>
       </c>
       <c r="E47" s="17" t="str">
+        <f t="shared" si="13"/>
+        <v>#define SPI_LEAK_RNDMASK 67</v>
+      </c>
+      <c r="F47" s="21" t="str">
         <f t="shared" si="11"/>
-        <v>#define SPI_LEAK_RNDMASK 67</v>
-      </c>
-      <c r="F47" s="21" t="str">
-        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_spi_leak_rndmask = 67;</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>140</v>
       </c>
       <c r="L47" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>980</v>
       </c>
       <c r="M47" s="5" t="s">
@@ -3348,11 +3368,11 @@
         <v>218</v>
       </c>
       <c r="Q47" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">#define BLOCK_WAVESET_5 980  // </v>
       </c>
       <c r="R47" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_waveset_5: Word = 980;  // </v>
       </c>
     </row>
@@ -3367,18 +3387,18 @@
         <v>8</v>
       </c>
       <c r="E48" s="17" t="str">
+        <f t="shared" si="13"/>
+        <v>#define SPI_DDS_TUNING 68</v>
+      </c>
+      <c r="F48" s="21" t="str">
         <f t="shared" si="11"/>
-        <v>#define SPI_DDS_TUNING 68</v>
-      </c>
-      <c r="F48" s="21" t="str">
-        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_spi_dds_tuning = 68;</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>138</v>
       </c>
       <c r="L48" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>984</v>
       </c>
       <c r="M48" s="5" t="s">
@@ -3391,11 +3411,11 @@
         <v>219</v>
       </c>
       <c r="Q48" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">#define BLOCK_WAVESET_6 984  // </v>
       </c>
       <c r="R48" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_waveset_6: Word = 984;  // </v>
       </c>
     </row>
@@ -3410,18 +3430,18 @@
         <v>8</v>
       </c>
       <c r="E49" s="17" t="str">
+        <f t="shared" si="13"/>
+        <v>#define SPI_AMP_IN_LVL 69</v>
+      </c>
+      <c r="F49" s="21" t="str">
         <f t="shared" si="11"/>
-        <v>#define SPI_AMP_IN_LVL 69</v>
-      </c>
-      <c r="F49" s="21" t="str">
-        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_spi_amp_in_lvl = 69;</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>124</v>
       </c>
       <c r="L49" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>988</v>
       </c>
       <c r="M49" s="5" t="s">
@@ -3434,11 +3454,11 @@
         <v>220</v>
       </c>
       <c r="Q49" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">#define BLOCK_WAVESET_7 988  // </v>
       </c>
       <c r="R49" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_waveset_7: Word = 988;  // </v>
       </c>
     </row>
@@ -3453,11 +3473,11 @@
         <v>8</v>
       </c>
       <c r="E50" s="17" t="str">
+        <f t="shared" si="13"/>
+        <v>#define SPI_AMP_OUT_LVL 70</v>
+      </c>
+      <c r="F50" s="21" t="str">
         <f t="shared" si="11"/>
-        <v>#define SPI_AMP_OUT_LVL 70</v>
-      </c>
-      <c r="F50" s="21" t="str">
-        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_spi_amp_out_lvl = 70;</v>
       </c>
       <c r="G50" s="5" t="s">
@@ -3479,11 +3499,11 @@
         <v>256</v>
       </c>
       <c r="Q50" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>#define BLOCK_FIRMWARE 992  // Buffer für Update</v>
       </c>
       <c r="R50" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_firmware: Word = 992;  // Buffer für Update</v>
       </c>
     </row>
@@ -3498,11 +3518,11 @@
         <v>8</v>
       </c>
       <c r="E51" s="17" t="str">
+        <f t="shared" si="13"/>
+        <v>#define SPI_NC 71</v>
+      </c>
+      <c r="F51" s="21" t="str">
         <f t="shared" si="11"/>
-        <v>#define SPI_NC 71</v>
-      </c>
-      <c r="F51" s="21" t="str">
-        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_spi_nc = 71;</v>
       </c>
     </row>
@@ -3517,11 +3537,11 @@
         <v>8</v>
       </c>
       <c r="E52" s="17" t="str">
+        <f t="shared" si="13"/>
+        <v>#define SPI_MASTER_VOLUME 72</v>
+      </c>
+      <c r="F52" s="21" t="str">
         <f t="shared" si="11"/>
-        <v>#define SPI_MASTER_VOLUME 72</v>
-      </c>
-      <c r="F52" s="21" t="str">
-        <f t="shared" si="9"/>
         <v xml:space="preserve">  c_spi_master_volume = 72;</v>
       </c>
       <c r="G52" s="5" t="s">
@@ -3560,11 +3580,11 @@
         <v>8</v>
       </c>
       <c r="E57" s="17" t="str">
-        <f t="shared" ref="E57:E66" si="13">CONCATENATE("#define SPI_",UPPER(SUBSTITUTE(C57," ","_"))," ",A57)</f>
+        <f t="shared" ref="E57:E66" si="15">CONCATENATE("#define SPI_",UPPER(SUBSTITUTE(C57," ","_"))," ",A57)</f>
         <v>#define SPI_AO28_LOUDN_BASS 80</v>
       </c>
       <c r="F57" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_ao28_loudn_bass = 80;</v>
       </c>
       <c r="G57" s="5" t="s">
@@ -3583,11 +3603,11 @@
         <v>8</v>
       </c>
       <c r="E58" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>#define SPI_AO28_MIDRANGE 81</v>
       </c>
       <c r="F58" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_ao28_midrange = 81;</v>
       </c>
       <c r="Q58" s="17"/>
@@ -3603,11 +3623,11 @@
         <v>8</v>
       </c>
       <c r="E59" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>#define SPI_AO28_LOUDN_TREBLE 82</v>
       </c>
       <c r="F59" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_ao28_loudn_treble = 82;</v>
       </c>
       <c r="Q59" s="17"/>
@@ -3623,11 +3643,11 @@
         <v>8</v>
       </c>
       <c r="E60" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>#define SPI_AO28_MIDRANGE_SHELF 83</v>
       </c>
       <c r="F60" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_ao28_midrange_shelf = 83;</v>
       </c>
       <c r="Q60" s="17"/>
@@ -3643,11 +3663,11 @@
         <v>8</v>
       </c>
       <c r="E61" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>#define SPI_AO28_FINAL_GAIN 84</v>
       </c>
       <c r="F61" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_ao28_final_gain = 84;</v>
       </c>
       <c r="Q61" s="17"/>
@@ -3663,11 +3683,11 @@
         <v>8</v>
       </c>
       <c r="E62" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>#define SPI_AO28_TRIODE_K2 85</v>
       </c>
       <c r="F62" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_ao28_triode_k2 = 85;</v>
       </c>
     </row>
@@ -3682,11 +3702,11 @@
         <v>8</v>
       </c>
       <c r="E63" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>#define SPI_AO28_PEDAL_LVL 86</v>
       </c>
       <c r="F63" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_ao28_pedal_lvl = 86;</v>
       </c>
     </row>
@@ -3701,11 +3721,11 @@
         <v>8</v>
       </c>
       <c r="E64" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>#define SPI_AO28_FREQU_RESPONSE_FINAL 87</v>
       </c>
       <c r="F64" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_ao28_frequ_response_final = 87;</v>
       </c>
       <c r="Q64" s="17"/>
@@ -3721,11 +3741,11 @@
         <v>8</v>
       </c>
       <c r="E65" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>#define SPI_AO28_FREQU_RESPONSE_MIDRANGE 88</v>
       </c>
       <c r="F65" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_ao28_frequ_response_midrange = 88;</v>
       </c>
       <c r="Q65" s="17"/>
@@ -3741,11 +3761,11 @@
         <v>8</v>
       </c>
       <c r="E66" s="17" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>#define SPI_AO28_BYPASS_SEL 89</v>
       </c>
       <c r="F66" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_ao28_bypass_sel = 89;</v>
       </c>
       <c r="G66" s="5" t="s">
@@ -3782,11 +3802,11 @@
         <v>8</v>
       </c>
       <c r="E71" s="17" t="str">
-        <f t="shared" ref="E71:E88" si="14">CONCATENATE("#define SPI_",UPPER(SUBSTITUTE(C71," ","_"))," ",A71)</f>
+        <f t="shared" ref="E71:E88" si="16">CONCATENATE("#define SPI_",UPPER(SUBSTITUTE(C71," ","_"))," ",A71)</f>
         <v>#define SPI_PHR_SPEED_SLOW 112</v>
       </c>
       <c r="F71" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_phr_speed_slow = 112;</v>
       </c>
     </row>
@@ -3801,11 +3821,11 @@
         <v>8</v>
       </c>
       <c r="E72" s="17" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>#define SPI_PHR_SPEED_FAST 113</v>
       </c>
       <c r="F72" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_phr_speed_fast = 113;</v>
       </c>
     </row>
@@ -3820,11 +3840,11 @@
         <v>8</v>
       </c>
       <c r="E73" s="17" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>#define SPI_PHR_SPEED_SLOW_FIXED 114</v>
       </c>
       <c r="F73" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_phr_speed_slow_fixed = 114;</v>
       </c>
     </row>
@@ -3839,11 +3859,11 @@
         <v>8</v>
       </c>
       <c r="E74" s="17" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>#define SPI_PHR_FEEDBACK_ 115</v>
       </c>
       <c r="F74" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_phr_feedback_ = 115;</v>
       </c>
     </row>
@@ -3858,11 +3878,11 @@
         <v>8</v>
       </c>
       <c r="E75" s="17" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>#define SPI_PHR_LEVEL_PH1_ 116</v>
       </c>
       <c r="F75" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_phr_level_ph1_ = 116;</v>
       </c>
     </row>
@@ -3877,11 +3897,11 @@
         <v>8</v>
       </c>
       <c r="E76" s="17" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>#define SPI_PHR_LEVEL_PH2_ 117</v>
       </c>
       <c r="F76" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_phr_level_ph2_ = 117;</v>
       </c>
     </row>
@@ -3896,11 +3916,11 @@
         <v>8</v>
       </c>
       <c r="E77" s="17" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>#define SPI_PHR_LEVEL_PH3_ 118</v>
       </c>
       <c r="F77" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_phr_level_ph3_ = 118;</v>
       </c>
     </row>
@@ -3915,11 +3935,11 @@
         <v>8</v>
       </c>
       <c r="E78" s="17" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>#define SPI_PHR_LEVEL_DRY_ 119</v>
       </c>
       <c r="F78" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_phr_level_dry_ = 119;</v>
       </c>
     </row>
@@ -3934,11 +3954,11 @@
         <v>8</v>
       </c>
       <c r="E79" s="17" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>#define SPI_PHR_FEEDBACK_SELECT_ 120</v>
       </c>
       <c r="F79" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_phr_feedback_select_ = 120;</v>
       </c>
     </row>
@@ -3953,11 +3973,11 @@
         <v>8</v>
       </c>
       <c r="E80" s="17" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>#define SPI_PHR_RAMP_DELAY_ 121</v>
       </c>
       <c r="F80" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_phr_ramp_delay_ = 121;</v>
       </c>
     </row>
@@ -3972,11 +3992,11 @@
         <v>8</v>
       </c>
       <c r="E81" s="17" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>#define SPI_PHR_MOD_VARI_PH1_ 122</v>
       </c>
       <c r="F81" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_phr_mod_vari_ph1_ = 122;</v>
       </c>
     </row>
@@ -3991,11 +4011,11 @@
         <v>8</v>
       </c>
       <c r="E82" s="17" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>#define SPI_PHR_MOD_VARI_PH2_ 123</v>
       </c>
       <c r="F82" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_phr_mod_vari_ph2_ = 123;</v>
       </c>
     </row>
@@ -4010,11 +4030,11 @@
         <v>8</v>
       </c>
       <c r="E83" s="17" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>#define SPI_PHR_MOD_VARI_PH3_ 124</v>
       </c>
       <c r="F83" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_phr_mod_vari_ph3_ = 124;</v>
       </c>
     </row>
@@ -4029,11 +4049,11 @@
         <v>8</v>
       </c>
       <c r="E84" s="17" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>#define SPI_PHR_MOD_SLOW_PH1_ 125</v>
       </c>
       <c r="F84" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_phr_mod_slow_ph1_ = 125;</v>
       </c>
     </row>
@@ -4048,11 +4068,11 @@
         <v>8</v>
       </c>
       <c r="E85" s="17" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>#define SPI_PHR_MOD_SLOW_PH2_ 126</v>
       </c>
       <c r="F85" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_phr_mod_slow_ph2_ = 126;</v>
       </c>
     </row>
@@ -4067,11 +4087,11 @@
         <v>8</v>
       </c>
       <c r="E86" s="17" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>#define SPI_PHR_MOD_SLOW_PH3_ 127</v>
       </c>
       <c r="F86" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_phr_mod_slow_ph3_ = 127;</v>
       </c>
     </row>
@@ -4086,11 +4106,11 @@
         <v>32</v>
       </c>
       <c r="E87" s="17" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>#define SPI_INC_LOADCORE 128</v>
       </c>
       <c r="F87" s="21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">  c_spi_inc_loadcore = 128;</v>
       </c>
       <c r="G87" s="5" t="s">
@@ -4108,11 +4128,11 @@
         <v>32</v>
       </c>
       <c r="E88" s="17" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>#define SPI_RST_LOADCORE 129</v>
       </c>
       <c r="F88" s="21" t="str">
-        <f t="shared" ref="F88:F151" si="15">CONCATENATE("  c_spi_",LOWER(SUBSTITUTE(C88," ","_"))," = ",A88,";")</f>
+        <f t="shared" ref="F88:F151" si="17">CONCATENATE("  c_spi_",LOWER(SUBSTITUTE(C88," ","_"))," = ",A88,";")</f>
         <v xml:space="preserve">  c_spi_rst_loadcore = 129;</v>
       </c>
       <c r="G88" s="5" t="s">
@@ -4148,11 +4168,11 @@
         <v>8</v>
       </c>
       <c r="E93" s="17" t="str">
-        <f t="shared" ref="E93:E104" si="16">CONCATENATE("#define SPI_",UPPER(SUBSTITUTE(C93," ","_"))," ",A93)</f>
+        <f t="shared" ref="E93:E104" si="18">CONCATENATE("#define SPI_",UPPER(SUBSTITUTE(C93," ","_"))," ",A93)</f>
         <v>#define SPI_VIB_PREEMPH 144</v>
       </c>
       <c r="F93" s="21" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">  c_spi_vib_preemph = 144;</v>
       </c>
       <c r="G93" s="5" t="s">
@@ -4170,11 +4190,11 @@
         <v>8</v>
       </c>
       <c r="E94" s="17" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>#define SPI_VIB_LC_LINE_AGE 145</v>
       </c>
       <c r="F94" s="21" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">  c_spi_vib_lc_line_age = 145;</v>
       </c>
       <c r="G94" s="5" t="s">
@@ -4192,11 +4212,11 @@
         <v>8</v>
       </c>
       <c r="E95" s="17" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>#define SPI_VIB_LC_LINE_FB 146</v>
       </c>
       <c r="F95" s="21" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">  c_spi_vib_lc_line_fb = 146;</v>
       </c>
       <c r="G95" s="5" t="s">
@@ -4214,11 +4234,11 @@
         <v>8</v>
       </c>
       <c r="E96" s="17" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>#define SPI_VIB_LC_LINE_REFLE 147</v>
       </c>
       <c r="F96" s="21" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">  c_spi_vib_lc_line_refle = 147;</v>
       </c>
       <c r="G96" s="5" t="s">
@@ -4236,11 +4256,11 @@
         <v>8</v>
       </c>
       <c r="E97" s="17" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>#define SPI_VIB_LC_LINE_CUTOFF 148</v>
       </c>
       <c r="F97" s="21" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">  c_spi_vib_lc_line_cutoff = 148;</v>
       </c>
       <c r="G97" s="5" t="s">
@@ -4258,11 +4278,11 @@
         <v>8</v>
       </c>
       <c r="E98" s="17" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>#define SPI_VIB_PHASELK_SHELV 149</v>
       </c>
       <c r="F98" s="21" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">  c_spi_vib_phaselk_shelv = 149;</v>
       </c>
       <c r="G98" s="5" t="s">
@@ -4280,11 +4300,11 @@
         <v>8</v>
       </c>
       <c r="E99" s="17" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>#define SPI_VIB_GEARING 150</v>
       </c>
       <c r="F99" s="21" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">  c_spi_vib_gearing = 150;</v>
       </c>
       <c r="G99" s="5" t="s">
@@ -4302,11 +4322,11 @@
         <v>8</v>
       </c>
       <c r="E100" s="17" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>#define SPI_VIB_DRY_LVL 151</v>
       </c>
       <c r="F100" s="21" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">  c_spi_vib_dry_lvl = 151;</v>
       </c>
       <c r="G100" s="5" t="s">
@@ -4324,11 +4344,11 @@
         <v>8</v>
       </c>
       <c r="E101" s="17" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>#define SPI_VIB_WET_LVL 152</v>
       </c>
       <c r="F101" s="21" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">  c_spi_vib_wet_lvl = 152;</v>
       </c>
       <c r="G101" s="5" t="s">
@@ -4346,11 +4366,11 @@
         <v>8</v>
       </c>
       <c r="E102" s="17" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>#define SPI_VIB_FLUTTER 153</v>
       </c>
       <c r="F102" s="21" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">  c_spi_vib_flutter = 153;</v>
       </c>
       <c r="G102" s="5" t="s">
@@ -4368,11 +4388,11 @@
         <v>8</v>
       </c>
       <c r="E103" s="17" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>#define SPI_VIB_PREMPH_FREQU 154</v>
       </c>
       <c r="F103" s="21" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">  c_spi_vib_premph_frequ = 154;</v>
       </c>
       <c r="G103" s="5" t="s">
@@ -4390,11 +4410,11 @@
         <v>8</v>
       </c>
       <c r="E104" s="17" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>#define SPI_VIB_MODWAVE_PHASE 155</v>
       </c>
       <c r="F104" s="21" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">  c_spi_vib_modwave_phase = 155;</v>
       </c>
       <c r="G104" s="5" t="s">
@@ -4436,11 +4456,11 @@
         <v>8</v>
       </c>
       <c r="E109" s="17" t="str">
-        <f t="shared" ref="E109:E153" si="17">CONCATENATE("#define SPI_",UPPER(SUBSTITUTE(C109," ","_"))," ",A109)</f>
+        <f t="shared" ref="E109:E153" si="19">CONCATENATE("#define SPI_",UPPER(SUBSTITUTE(C109," ","_"))," ",A109)</f>
         <v>#define SPI_LC_LINE_DLY_0 160</v>
       </c>
       <c r="F109" s="21" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">  c_spi_lc_line_dly_0 = 160;</v>
       </c>
       <c r="G109" s="5" t="s">
@@ -4458,11 +4478,11 @@
         <v>8</v>
       </c>
       <c r="E110" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_LC_LINE_DLY_1 161</v>
+      </c>
+      <c r="F110" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_LC_LINE_DLY_1 161</v>
-      </c>
-      <c r="F110" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lc_line_dly_1 = 161;</v>
       </c>
     </row>
@@ -4477,11 +4497,11 @@
         <v>8</v>
       </c>
       <c r="E111" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_LC_LINE_DLY_2 162</v>
+      </c>
+      <c r="F111" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_LC_LINE_DLY_2 162</v>
-      </c>
-      <c r="F111" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lc_line_dly_2 = 162;</v>
       </c>
     </row>
@@ -4496,11 +4516,11 @@
         <v>8</v>
       </c>
       <c r="E112" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_LC_LINE_DLY_3 163</v>
+      </c>
+      <c r="F112" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_LC_LINE_DLY_3 163</v>
-      </c>
-      <c r="F112" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lc_line_dly_3 = 163;</v>
       </c>
     </row>
@@ -4515,11 +4535,11 @@
         <v>8</v>
       </c>
       <c r="E113" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_LC_LINE_DLY_4 164</v>
+      </c>
+      <c r="F113" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_LC_LINE_DLY_4 164</v>
-      </c>
-      <c r="F113" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lc_line_dly_4 = 164;</v>
       </c>
     </row>
@@ -4534,11 +4554,11 @@
         <v>8</v>
       </c>
       <c r="E114" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_LC_LINE_DLY_5 165</v>
+      </c>
+      <c r="F114" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_LC_LINE_DLY_5 165</v>
-      </c>
-      <c r="F114" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lc_line_dly_5 = 165;</v>
       </c>
     </row>
@@ -4553,11 +4573,11 @@
         <v>8</v>
       </c>
       <c r="E115" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_LC_LINE_DLY_6 166</v>
+      </c>
+      <c r="F115" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_LC_LINE_DLY_6 166</v>
-      </c>
-      <c r="F115" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lc_line_dly_6 = 166;</v>
       </c>
     </row>
@@ -4572,11 +4592,11 @@
         <v>8</v>
       </c>
       <c r="E116" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_LC_LINE_DLY_7 167</v>
+      </c>
+      <c r="F116" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_LC_LINE_DLY_7 167</v>
-      </c>
-      <c r="F116" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lc_line_dly_7 = 167;</v>
       </c>
     </row>
@@ -4591,11 +4611,11 @@
         <v>8</v>
       </c>
       <c r="E117" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_LC_LINE_DLY_8 168</v>
+      </c>
+      <c r="F117" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_LC_LINE_DLY_8 168</v>
-      </c>
-      <c r="F117" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lc_line_dly_8 = 168;</v>
       </c>
     </row>
@@ -4610,11 +4630,11 @@
         <v>8</v>
       </c>
       <c r="E118" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_LC_LINE_DLY_9 169</v>
+      </c>
+      <c r="F118" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_LC_LINE_DLY_9 169</v>
-      </c>
-      <c r="F118" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lc_line_dly_9 = 169;</v>
       </c>
     </row>
@@ -4629,11 +4649,11 @@
         <v>8</v>
       </c>
       <c r="E119" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_LC_LINE_DLY_10 170</v>
+      </c>
+      <c r="F119" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_LC_LINE_DLY_10 170</v>
-      </c>
-      <c r="F119" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lc_line_dly_10 = 170;</v>
       </c>
     </row>
@@ -4648,11 +4668,11 @@
         <v>8</v>
       </c>
       <c r="E120" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_LC_LINE_DLY_11 171</v>
+      </c>
+      <c r="F120" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_LC_LINE_DLY_11 171</v>
-      </c>
-      <c r="F120" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lc_line_dly_11 = 171;</v>
       </c>
     </row>
@@ -4667,11 +4687,11 @@
         <v>8</v>
       </c>
       <c r="E121" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_LC_LINE_DLY_12 172</v>
+      </c>
+      <c r="F121" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_LC_LINE_DLY_12 172</v>
-      </c>
-      <c r="F121" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lc_line_dly_12 = 172;</v>
       </c>
     </row>
@@ -4686,11 +4706,11 @@
         <v>8</v>
       </c>
       <c r="E122" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_LC_LINE_DLY_13 173</v>
+      </c>
+      <c r="F122" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_LC_LINE_DLY_13 173</v>
-      </c>
-      <c r="F122" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lc_line_dly_13 = 173;</v>
       </c>
     </row>
@@ -4705,11 +4725,11 @@
         <v>8</v>
       </c>
       <c r="E123" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_LC_LINE_DLY_14 174</v>
+      </c>
+      <c r="F123" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_LC_LINE_DLY_14 174</v>
-      </c>
-      <c r="F123" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lc_line_dly_14 = 174;</v>
       </c>
     </row>
@@ -4749,11 +4769,11 @@
         <v>8</v>
       </c>
       <c r="E126" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_SPEED_HORN 177</v>
+      </c>
+      <c r="F126" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_SPEED_HORN 177</v>
-      </c>
-      <c r="F126" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_speed_horn = 177;</v>
       </c>
       <c r="I126" s="5" t="s">
@@ -4771,11 +4791,11 @@
         <v>8</v>
       </c>
       <c r="E127" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_SPEED_ROTOR 178</v>
+      </c>
+      <c r="F127" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_SPEED_ROTOR 178</v>
-      </c>
-      <c r="F127" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_speed_rotor = 178;</v>
       </c>
       <c r="I127" s="5" t="s">
@@ -4793,11 +4813,11 @@
         <v>8</v>
       </c>
       <c r="E128" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_NOT_USED 179</v>
+      </c>
+      <c r="F128" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_NOT_USED 179</v>
-      </c>
-      <c r="F128" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_not_used = 179;</v>
       </c>
       <c r="G128" s="5" t="s">
@@ -4818,11 +4838,11 @@
         <v>8</v>
       </c>
       <c r="E129" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_ROTRY_INP_LVL 180</v>
+      </c>
+      <c r="F129" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_ROTRY_INP_LVL 180</v>
-      </c>
-      <c r="F129" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_rotry_inp_lvl = 180;</v>
       </c>
       <c r="I129" s="5" t="s">
@@ -4840,11 +4860,11 @@
         <v>8</v>
       </c>
       <c r="E130" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_ROTRY_HORN_LVL 181</v>
+      </c>
+      <c r="F130" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_ROTRY_HORN_LVL 181</v>
-      </c>
-      <c r="F130" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_rotry_horn_lvl = 181;</v>
       </c>
       <c r="I130" s="5" t="s">
@@ -4862,11 +4882,11 @@
         <v>8</v>
       </c>
       <c r="E131" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_ROTRY_ROTOR_LVL 182</v>
+      </c>
+      <c r="F131" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_ROTRY_ROTOR_LVL 182</v>
-      </c>
-      <c r="F131" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_rotry_rotor_lvl = 182;</v>
       </c>
       <c r="I131" s="5" t="s">
@@ -4884,11 +4904,11 @@
         <v>8</v>
       </c>
       <c r="E132" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_ROTRY_HORN_NEAR_REFL_LVL 183</v>
+      </c>
+      <c r="F132" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_ROTRY_HORN_NEAR_REFL_LVL 183</v>
-      </c>
-      <c r="F132" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_rotry_horn_near_refl_lvl = 183;</v>
       </c>
       <c r="I132" s="5" t="s">
@@ -4906,11 +4926,11 @@
         <v>8</v>
       </c>
       <c r="E133" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_ROTRY_HORN_ROOM_REFL_LVL 184</v>
+      </c>
+      <c r="F133" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_ROTRY_HORN_ROOM_REFL_LVL 184</v>
-      </c>
-      <c r="F133" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_rotry_horn_room_refl_lvl = 184;</v>
       </c>
       <c r="I133" s="5" t="s">
@@ -4928,11 +4948,11 @@
         <v>8</v>
       </c>
       <c r="E134" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_ROTRY_XOVER_FREQU 185</v>
+      </c>
+      <c r="F134" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_ROTRY_XOVER_FREQU 185</v>
-      </c>
-      <c r="F134" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_rotry_xover_frequ = 185;</v>
       </c>
       <c r="I134" s="5" t="s">
@@ -4966,11 +4986,11 @@
         <v>8</v>
       </c>
       <c r="E136" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_ROTRY_PRE_DLY 187</v>
+      </c>
+      <c r="F136" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_ROTRY_PRE_DLY 187</v>
-      </c>
-      <c r="F136" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_rotry_pre_dly = 187;</v>
       </c>
       <c r="I136" s="5" t="s">
@@ -4988,11 +5008,11 @@
         <v>8</v>
       </c>
       <c r="E137" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_ROTRY_DIFFUSE_1 188</v>
+      </c>
+      <c r="F137" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_ROTRY_DIFFUSE_1 188</v>
-      </c>
-      <c r="F137" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_rotry_diffuse_1 = 188;</v>
       </c>
       <c r="I137" s="5" t="s">
@@ -5010,11 +5030,11 @@
         <v>8</v>
       </c>
       <c r="E138" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_ROTRY_DIFFUSE_2 189</v>
+      </c>
+      <c r="F138" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_ROTRY_DIFFUSE_2 189</v>
-      </c>
-      <c r="F138" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_rotry_diffuse_2 = 189;</v>
       </c>
       <c r="I138" s="5" t="s">
@@ -5032,11 +5052,11 @@
         <v>8</v>
       </c>
       <c r="E139" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_ROTRY_DIFFUSE_3 190</v>
+      </c>
+      <c r="F139" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_ROTRY_DIFFUSE_3 190</v>
-      </c>
-      <c r="F139" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_rotry_diffuse_3 = 190;</v>
       </c>
       <c r="I139" s="5" t="s">
@@ -5054,11 +5074,11 @@
         <v>8</v>
       </c>
       <c r="E140" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_ROTRY_DIFFUSE_4 191</v>
+      </c>
+      <c r="F140" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_ROTRY_DIFFUSE_4 191</v>
-      </c>
-      <c r="F140" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_rotry_diffuse_4 = 191;</v>
       </c>
       <c r="I140" s="5" t="s">
@@ -5076,11 +5096,11 @@
         <v>8</v>
       </c>
       <c r="E141" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_LFO_MOD_HORN_MAIN_L 192</v>
+      </c>
+      <c r="F141" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_LFO_MOD_HORN_MAIN_L 192</v>
-      </c>
-      <c r="F141" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lfo_mod_horn_main_l = 192;</v>
       </c>
       <c r="G141" s="5" t="s">
@@ -5101,11 +5121,11 @@
         <v>8</v>
       </c>
       <c r="E142" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_LFO_MOD_HORN_MAIN_R 193</v>
+      </c>
+      <c r="F142" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_LFO_MOD_HORN_MAIN_R 193</v>
-      </c>
-      <c r="F142" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lfo_mod_horn_main_r = 193;</v>
       </c>
       <c r="I142" s="27" t="s">
@@ -5126,11 +5146,11 @@
         <v>8</v>
       </c>
       <c r="E143" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_LFO_MOD_HORN_REFL_1_L_NEAR 194</v>
+      </c>
+      <c r="F143" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_LFO_MOD_HORN_REFL_1_L_NEAR 194</v>
-      </c>
-      <c r="F143" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lfo_mod_horn_refl_1_l_near = 194;</v>
       </c>
       <c r="I143" s="5" t="s">
@@ -5148,11 +5168,11 @@
         <v>8</v>
       </c>
       <c r="E144" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_LFO_MOD_HORN_REFL_1_R_NEAR 195</v>
+      </c>
+      <c r="F144" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_LFO_MOD_HORN_REFL_1_R_NEAR 195</v>
-      </c>
-      <c r="F144" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lfo_mod_horn_refl_1_r_near = 195;</v>
       </c>
       <c r="I144" s="27" t="s">
@@ -5173,11 +5193,11 @@
         <v>8</v>
       </c>
       <c r="E145" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_LFO_MOD_HORN_REFL_2_L_FAR 196</v>
+      </c>
+      <c r="F145" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_LFO_MOD_HORN_REFL_2_L_FAR 196</v>
-      </c>
-      <c r="F145" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lfo_mod_horn_refl_2_l_far = 196;</v>
       </c>
       <c r="I145" s="5" t="s">
@@ -5195,11 +5215,11 @@
         <v>8</v>
       </c>
       <c r="E146" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_LFO_MOD_HORN_REFL_2_R_FAR 197</v>
+      </c>
+      <c r="F146" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_LFO_MOD_HORN_REFL_2_R_FAR 197</v>
-      </c>
-      <c r="F146" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lfo_mod_horn_refl_2_r_far = 197;</v>
       </c>
       <c r="I146" s="27" t="s">
@@ -5220,11 +5240,11 @@
         <v>8</v>
       </c>
       <c r="E147" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_LFO_MOD_HORN_THROB_L 198</v>
+      </c>
+      <c r="F147" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_LFO_MOD_HORN_THROB_L 198</v>
-      </c>
-      <c r="F147" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lfo_mod_horn_throb_l = 198;</v>
       </c>
       <c r="I147" s="5" t="s">
@@ -5242,11 +5262,11 @@
         <v>8</v>
       </c>
       <c r="E148" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_LFO_MOD_HORN_THROB_R 199</v>
+      </c>
+      <c r="F148" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_LFO_MOD_HORN_THROB_R 199</v>
-      </c>
-      <c r="F148" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lfo_mod_horn_throb_r = 199;</v>
       </c>
       <c r="I148" s="27" t="s">
@@ -5267,11 +5287,11 @@
         <v>8</v>
       </c>
       <c r="E149" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_LFO_MOD_HORN_CAB 200</v>
+      </c>
+      <c r="F149" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_LFO_MOD_HORN_CAB 200</v>
-      </c>
-      <c r="F149" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lfo_mod_horn_cab = 200;</v>
       </c>
       <c r="I149" s="5" t="s">
@@ -5289,11 +5309,11 @@
         <v>8</v>
       </c>
       <c r="E150" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_LFO_MOD_ROTOR_MAIN 201</v>
+      </c>
+      <c r="F150" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_LFO_MOD_ROTOR_MAIN 201</v>
-      </c>
-      <c r="F150" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lfo_mod_rotor_main = 201;</v>
       </c>
       <c r="I150" s="5" t="s">
@@ -5311,11 +5331,11 @@
         <v>8</v>
       </c>
       <c r="E151" s="17" t="str">
+        <f t="shared" si="19"/>
+        <v>#define SPI_LFO_MOD_ROTOR_REFL 202</v>
+      </c>
+      <c r="F151" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>#define SPI_LFO_MOD_ROTOR_REFL 202</v>
-      </c>
-      <c r="F151" s="21" t="str">
-        <f t="shared" si="15"/>
         <v xml:space="preserve">  c_spi_lfo_mod_rotor_refl = 202;</v>
       </c>
       <c r="I151" s="5" t="s">
@@ -5333,11 +5353,11 @@
         <v>8</v>
       </c>
       <c r="E152" s="17" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>#define SPI_LFO_MOD_ROTOR_THROB 203</v>
       </c>
       <c r="F152" s="21" t="str">
-        <f t="shared" ref="F152:F170" si="18">CONCATENATE("  c_spi_",LOWER(SUBSTITUTE(C152," ","_"))," = ",A152,";")</f>
+        <f t="shared" ref="F152:F170" si="20">CONCATENATE("  c_spi_",LOWER(SUBSTITUTE(C152," ","_"))," = ",A152,";")</f>
         <v xml:space="preserve">  c_spi_lfo_mod_rotor_throb = 203;</v>
       </c>
       <c r="G152" s="10"/>
@@ -5356,11 +5376,11 @@
         <v>8</v>
       </c>
       <c r="E153" s="17" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>#define SPI_HORN_FIR_FILTER_ENABLE 204</v>
       </c>
       <c r="F153" s="21" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">  c_spi_horn_fir_filter_enable = 204;</v>
       </c>
       <c r="G153" s="5" t="s">
@@ -5405,11 +5425,11 @@
         <v>8</v>
       </c>
       <c r="E159" s="17" t="str">
-        <f t="shared" ref="E159:E170" si="19">CONCATENATE("#define SPI_",UPPER(SUBSTITUTE(C159," ","_"))," ",A159)</f>
+        <f t="shared" ref="E159:E170" si="21">CONCATENATE("#define SPI_",UPPER(SUBSTITUTE(C159," ","_"))," ",A159)</f>
         <v>#define SPI_LFO_PHASE_OFFSET_HORN_MAIN_L 224</v>
       </c>
       <c r="F159" s="21" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">  c_spi_lfo_phase_offset_horn_main_l = 224;</v>
       </c>
       <c r="G159" s="5" t="s">
@@ -5430,11 +5450,11 @@
         <v>8</v>
       </c>
       <c r="E160" s="17" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#define SPI_LFO_PHASE_OFFSET_HORN_MAIN_R 225</v>
       </c>
       <c r="F160" s="21" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">  c_spi_lfo_phase_offset_horn_main_r = 225;</v>
       </c>
       <c r="I160" s="27" t="s">
@@ -5455,11 +5475,11 @@
         <v>8</v>
       </c>
       <c r="E161" s="17" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#define SPI_LFO_PHASE_OFFSET_HORN_REFL_1_L_NEAR_CAB 226</v>
       </c>
       <c r="F161" s="21" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">  c_spi_lfo_phase_offset_horn_refl_1_l_near_cab = 226;</v>
       </c>
       <c r="I161" s="5" t="s">
@@ -5477,11 +5497,11 @@
         <v>8</v>
       </c>
       <c r="E162" s="17" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#define SPI_LFO_PHASE_OFFSET_HORN_REFL_1_R_NEAR_CAB 227</v>
       </c>
       <c r="F162" s="21" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">  c_spi_lfo_phase_offset_horn_refl_1_r_near_cab = 227;</v>
       </c>
       <c r="I162" s="27" t="s">
@@ -5502,11 +5522,11 @@
         <v>8</v>
       </c>
       <c r="E163" s="17" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#define SPI_LFO_PHASE_OFFSET_HORN_REFL_2_L__FAR 228</v>
       </c>
       <c r="F163" s="21" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">  c_spi_lfo_phase_offset_horn_refl_2_l__far = 228;</v>
       </c>
       <c r="I163" s="5" t="s">
@@ -5524,11 +5544,11 @@
         <v>8</v>
       </c>
       <c r="E164" s="17" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#define SPI_LFO_PHASE_OFFSET_HORN_REFL_2_R_FAR 229</v>
       </c>
       <c r="F164" s="21" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">  c_spi_lfo_phase_offset_horn_refl_2_r_far = 229;</v>
       </c>
       <c r="I164" s="27" t="s">
@@ -5549,11 +5569,11 @@
         <v>8</v>
       </c>
       <c r="E165" s="17" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#define SPI_LFO_PHASE_OFFSET_HORN_THROB_L__2_KHZ 230</v>
       </c>
       <c r="F165" s="21" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">  c_spi_lfo_phase_offset_horn_throb_l__2_khz = 230;</v>
       </c>
       <c r="I165" s="5" t="s">
@@ -5571,11 +5591,11 @@
         <v>8</v>
       </c>
       <c r="E166" s="17" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#define SPI_LFO_PHASE_OFFSET_HORN_THROB_R_2_KHZ 231</v>
       </c>
       <c r="F166" s="21" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">  c_spi_lfo_phase_offset_horn_throb_r_2_khz = 231;</v>
       </c>
       <c r="I166" s="27" t="s">
@@ -5596,11 +5616,11 @@
         <v>8</v>
       </c>
       <c r="E167" s="17" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#define SPI_LFO_PHASE_OFFSET_HORN_CAB_4X 232</v>
       </c>
       <c r="F167" s="21" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">  c_spi_lfo_phase_offset_horn_cab_4x = 232;</v>
       </c>
       <c r="I167" s="5" t="s">
@@ -5618,11 +5638,11 @@
         <v>8</v>
       </c>
       <c r="E168" s="17" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#define SPI_LFO_PHASE_OFFSET_ROTOR_MAIN 233</v>
       </c>
       <c r="F168" s="21" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">  c_spi_lfo_phase_offset_rotor_main = 233;</v>
       </c>
       <c r="I168" s="5" t="s">
@@ -5640,11 +5660,11 @@
         <v>8</v>
       </c>
       <c r="E169" s="17" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#define SPI_LFO_PHASE_OFFSET_ROTOR_REFL 234</v>
       </c>
       <c r="F169" s="21" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">  c_spi_lfo_phase_offset_rotor_refl = 234;</v>
       </c>
       <c r="I169" s="5" t="s">
@@ -5662,11 +5682,11 @@
         <v>8</v>
       </c>
       <c r="E170" s="17" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#define SPI_LFO_PHASE_OFFSET_ROTOR_THROB 235</v>
       </c>
       <c r="F170" s="21" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">  c_spi_lfo_phase_offset_rotor_throb = 235;</v>
       </c>
       <c r="I170" s="5" t="s">
@@ -5707,7 +5727,7 @@
         <v>32</v>
       </c>
       <c r="E175" s="17" t="str">
-        <f t="shared" ref="E175:E176" si="20">CONCATENATE("#define SPI_",UPPER(SUBSTITUTE(C175," ","_"))," ",A175)</f>
+        <f t="shared" ref="E175:E176" si="22">CONCATENATE("#define SPI_",UPPER(SUBSTITUTE(C175," ","_"))," ",A175)</f>
         <v>#define SPI_DNA_COMPARE_0 240</v>
       </c>
       <c r="F175" s="17" t="str">
@@ -5732,11 +5752,11 @@
         <v>32</v>
       </c>
       <c r="E176" s="17" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>#define SPI_DNA_COMPARE_1 241</v>
       </c>
       <c r="F176" s="17" t="str">
-        <f t="shared" ref="F176:F178" si="21">CONCATENATE("  c_spi_",LOWER(SUBSTITUTE(B176," ","_"))," = ",A176,";")</f>
+        <f t="shared" ref="F176:F178" si="23">CONCATENATE("  c_spi_",LOWER(SUBSTITUTE(B176," ","_"))," = ",A176,";")</f>
         <v xml:space="preserve">  c_spi_dna_compare_1 = 241;</v>
       </c>
       <c r="G176" s="5" t="s">
@@ -5758,7 +5778,7 @@
         <v>#define SPI_RD_DNA_0 242</v>
       </c>
       <c r="F177" s="17" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v xml:space="preserve">  c_spi_dna_0 = 242;</v>
       </c>
       <c r="G177" s="5" t="s">
@@ -5776,11 +5796,11 @@
         <v>32</v>
       </c>
       <c r="E178" s="17" t="str">
-        <f t="shared" ref="E178:E179" si="22">CONCATENATE("#define SPI_RD_",UPPER(SUBSTITUTE(B178," ","_"))," ",A178)</f>
+        <f t="shared" ref="E178:E179" si="24">CONCATENATE("#define SPI_RD_",UPPER(SUBSTITUTE(B178," ","_"))," ",A178)</f>
         <v>#define SPI_RD_DNA_1 243</v>
       </c>
       <c r="F178" s="17" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v xml:space="preserve">  c_spi_dna_1 = 243;</v>
       </c>
       <c r="G178" s="5" t="s">
@@ -5798,7 +5818,7 @@
         <v>32</v>
       </c>
       <c r="E179" s="17" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>#define SPI_RD_LIC_VALID 244</v>
       </c>
       <c r="F179" s="17" t="str">
@@ -5826,11 +5846,11 @@
         <v>32</v>
       </c>
       <c r="E181" s="17" t="str">
-        <f t="shared" ref="E181" si="23">CONCATENATE("#define SPI_",UPPER(SUBSTITUTE(C181," ","_"))," ",A181)</f>
+        <f t="shared" ref="E181" si="25">CONCATENATE("#define SPI_",UPPER(SUBSTITUTE(C181," ","_"))," ",A181)</f>
         <v>#define SPI_SAM_COMMAND 246</v>
       </c>
       <c r="F181" s="21" t="str">
-        <f t="shared" ref="F181" si="24">CONCATENATE("  c_spi_",LOWER(SUBSTITUTE(C181," ","_"))," = ",A181,";")</f>
+        <f t="shared" ref="F181" si="26">CONCATENATE("  c_spi_",LOWER(SUBSTITUTE(C181," ","_"))," = ",A181,";")</f>
         <v xml:space="preserve">  c_spi_sam_command = 246;</v>
       </c>
       <c r="G181" s="5" t="s">
